--- a/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
   <si>
     <t>LOVE</t>
   </si>
@@ -656,406 +656,419 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45228</v>
+      </c>
+      <c r="E7" s="2">
         <v>45137</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44955</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44864</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44682</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44591</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44409</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44318</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44136</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44045</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43954</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43863</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43772</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43681</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43590</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43499</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43408</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43317</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43226</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43135</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43037</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42946</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42855</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42582</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>154000</v>
+      </c>
+      <c r="E8" s="3">
         <v>154500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>141200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>238500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>134800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>148500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>129400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>196200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>116700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>102400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>82900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>129700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>74700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>61900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>54400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>92200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>52100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>48100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>41000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>64200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>41700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>33200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>26800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>39000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>24400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>20700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>17600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>30500</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E9" s="3">
         <v>62100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>70600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>104800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>69900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>69400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>63400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>173600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>58100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>43400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>36800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>54600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>33400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>30900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>27100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>47000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>25800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>23900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>20000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>28700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>18800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>15400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>16100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>10700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>9200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>14700</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>88400</v>
+      </c>
+      <c r="E10" s="3">
         <v>92400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>70600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>133700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>64900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>79100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>66000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>22600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>58600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>59000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>46100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>75100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>41300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>31000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>27300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>45200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>26300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>24200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>21000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>35500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>22900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>17800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>14700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>22900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>13700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>11500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>9100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>15800</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1087,8 +1100,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1176,8 +1190,11 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1265,8 +1282,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1288,24 +1308,24 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>-600</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>600</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1321,8 +1341,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1354,86 +1374,89 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E15" s="3">
         <v>3000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>700</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB15" s="3">
         <v>800</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1443,8 +1466,11 @@
       <c r="AE15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1473,186 +1499,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>157600</v>
+      </c>
+      <c r="E17" s="3">
         <v>155500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>146900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>202000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>144900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>140400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>126900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>169900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>113700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>93400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>80700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>107900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>72200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>63000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>62800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>86800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>59000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>53100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>50300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>55900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>44400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>40200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>32400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>36500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>26500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>23100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>20800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>36500</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>36500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>26300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>21800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-6900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>8300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1684,47 +1717,48 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1732,13 +1766,13 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
       </c>
       <c r="T20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U20" s="3">
         <v>200</v>
@@ -1750,10 +1784,10 @@
         <v>200</v>
       </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Y20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3">
         <v>-100</v>
@@ -1762,108 +1796,114 @@
         <v>-100</v>
       </c>
       <c r="AB20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>2400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>39100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>28400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>23300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-6700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-8000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1946,138 +1986,144 @@
         <v>0</v>
       </c>
       <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
         <v>300</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>36500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>26300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-6300</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-7900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -2117,8 +2163,8 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
+      <c r="AB24" s="3">
+        <v>0</v>
       </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
@@ -2129,8 +2175,11 @@
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2218,186 +2267,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>26200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>34200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>21700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>8400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-6300</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>26200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>34200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>8400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>21700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>8400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-33700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-6300</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2485,8 +2543,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2574,8 +2635,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2663,8 +2727,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2752,47 +2819,50 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2800,13 +2870,13 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
       </c>
       <c r="T32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="U32" s="3">
         <v>-200</v>
@@ -2818,10 +2888,10 @@
         <v>-200</v>
       </c>
       <c r="X32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="Y32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="3">
         <v>100</v>
@@ -2830,108 +2900,114 @@
         <v>100</v>
       </c>
       <c r="AB32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>100</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>26200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>34200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>21700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>8400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-33700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6300</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3019,191 +3095,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>26200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>34200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>21700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>8400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-33700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6300</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45228</v>
+      </c>
+      <c r="E38" s="2">
         <v>45137</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44955</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44864</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44682</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44591</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44409</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44318</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44136</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44045</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43954</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43863</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43772</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43681</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43590</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43499</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43408</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43317</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43226</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43135</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43037</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42946</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42855</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42582</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3235,8 +3320,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3268,83 +3354,84 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E41" s="3">
         <v>54700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>45100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>43500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>17700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>64400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>92400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>47900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>68500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>65700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>78300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>47700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>54800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>45500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>48500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>27900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>44200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>35700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>49100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>44700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>48200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9200</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3357,8 +3444,11 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3446,83 +3536,86 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E43" s="3">
         <v>8000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>18400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2800</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3535,83 +3628,86 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>116600</v>
+      </c>
+      <c r="E44" s="3">
         <v>105000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>104500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>119600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>154500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>145700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>123000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>108500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>94500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>75000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>56000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>50400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>57800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>41000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>33400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>36400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>50200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>40700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>30900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>26200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>24600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>20200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>13900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>11600</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3624,83 +3720,86 @@
       <c r="AE44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E45" s="3">
         <v>15900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>15500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>35600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>31200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6300</v>
-      </c>
-      <c r="X45" s="3">
-        <v>5800</v>
       </c>
       <c r="Y45" s="3">
         <v>5800</v>
       </c>
       <c r="Z45" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AA45" s="3">
         <v>6100</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3713,83 +3812,86 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>184300</v>
+      </c>
+      <c r="E46" s="3">
         <v>183600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>181500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>187700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>209300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>203500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>206200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>221700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>163600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>161400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>140200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>143400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>123500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>107800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>91900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>100200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>95400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>97500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>78000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>85100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>78500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>78300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>24900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>29700</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3802,8 +3904,11 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3891,83 +3996,86 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>212300</v>
+      </c>
+      <c r="E48" s="3">
         <v>212400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>202800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>188300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>179500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>155300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>145400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>135000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>127700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>118400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>117600</v>
-      </c>
-      <c r="N48" s="3">
-        <v>25900</v>
       </c>
       <c r="O48" s="3">
         <v>25900</v>
       </c>
       <c r="P48" s="3">
+        <v>25900</v>
+      </c>
+      <c r="Q48" s="3">
         <v>25700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>24400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>23800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>18600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>17100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>15700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11000</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3980,8 +4088,11 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3992,13 +4103,13 @@
         <v>1600</v>
       </c>
       <c r="F49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G49" s="3">
         <v>3000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2900</v>
-      </c>
-      <c r="H49" s="3">
-        <v>3000</v>
       </c>
       <c r="I49" s="3">
         <v>3000</v>
@@ -4007,55 +4118,55 @@
         <v>3000</v>
       </c>
       <c r="K49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L49" s="3">
         <v>1500</v>
-      </c>
-      <c r="L49" s="3">
-        <v>1300</v>
       </c>
       <c r="M49" s="3">
         <v>1300</v>
       </c>
       <c r="N49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O49" s="3">
         <v>1700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1200</v>
-      </c>
-      <c r="U49" s="3">
-        <v>1100</v>
       </c>
       <c r="V49" s="3">
         <v>1100</v>
       </c>
       <c r="W49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X49" s="3">
         <v>1000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>800</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>700</v>
       </c>
       <c r="Z49" s="3">
         <v>700</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>3</v>
+      <c r="AA49" s="3">
+        <v>700</v>
       </c>
       <c r="AB49" s="3" t="s">
         <v>3</v>
@@ -4069,8 +4180,11 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4158,8 +4272,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4247,40 +4364,43 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E52" s="3">
         <v>36000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>35300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>31000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10800</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
       <c r="M52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N52" s="3">
         <v>100</v>
@@ -4292,13 +4412,13 @@
         <v>100</v>
       </c>
       <c r="Q52" s="3">
+        <v>100</v>
+      </c>
+      <c r="R52" s="3">
         <v>200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>100</v>
-      </c>
-      <c r="S52" s="3">
-        <v>200</v>
       </c>
       <c r="T52" s="3">
         <v>200</v>
@@ -4313,16 +4433,16 @@
         <v>200</v>
       </c>
       <c r="X52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Y52" s="3">
         <v>300</v>
       </c>
       <c r="Z52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>0</v>
       </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
@@ -4336,8 +4456,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4425,83 +4548,86 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>436300</v>
+      </c>
+      <c r="E54" s="3">
         <v>433600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>421200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>408600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>401100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>368900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>363600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>369100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>292800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>281300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>259200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>171000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>151100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>135300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>118100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>125700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>118700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>119300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>98800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>105000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>96800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>95100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>39100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>41400</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4514,8 +4640,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4547,8 +4676,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4580,83 +4710,84 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>37200</v>
+      </c>
+      <c r="E57" s="3">
         <v>33900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>30100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>47300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>34200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>33200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>25400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>25900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>24300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>25200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>24500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>19900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>19000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>17700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>19800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>16800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>16900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>15300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12700</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4669,8 +4800,11 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4743,8 +4877,8 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
+      <c r="AA58" s="3">
+        <v>0</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
@@ -4758,83 +4892,86 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>68700</v>
+      </c>
+      <c r="E59" s="3">
         <v>63500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>59000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>57500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>64100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>58600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>69600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>81400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>56100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>54700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>46000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>32000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>34300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>23600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4000</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4847,83 +4984,86 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>105900</v>
+      </c>
+      <c r="E60" s="3">
         <v>97300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>89100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>82000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>111400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>92900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>99400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>114700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>81600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>80600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>63700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>56300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>59500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>48000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>32300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>32400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>31800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>27100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>27400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>24600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>25100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>21500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>18200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>16700</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4936,8 +5076,11 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5005,11 +5148,11 @@
         <v>0</v>
       </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>1500</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5025,83 +5168,86 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>144900</v>
+      </c>
+      <c r="E62" s="3">
         <v>149400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>142800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>133500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>130200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>109900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>103500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>96600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>90700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>83700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>84700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1700</v>
-      </c>
-      <c r="U62" s="3">
-        <v>1600</v>
       </c>
       <c r="V62" s="3">
         <v>1600</v>
       </c>
       <c r="W62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="X62" s="3">
         <v>1400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1100</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5114,8 +5260,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5203,8 +5352,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5292,8 +5444,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5381,83 +5536,86 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>250800</v>
+      </c>
+      <c r="E66" s="3">
         <v>246800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>232000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>215500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>241600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>202700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>202900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>211300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>172200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>164300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>148500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>63100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>65900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>53500</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>35500</v>
       </c>
       <c r="R66" s="3">
         <v>35500</v>
       </c>
       <c r="S66" s="3">
+        <v>35500</v>
+      </c>
+      <c r="T66" s="3">
         <v>34300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>28700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>29000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>26200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>26500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>22900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>20800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>17800</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5470,8 +5628,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5503,8 +5664,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5592,8 +5754,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5681,8 +5846,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5770,8 +5938,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5859,83 +6030,86 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E72" s="3">
         <v>5800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-15700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-8300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-14200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-15900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-50200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-52900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-61400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-63400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-85100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-87600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-86500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-78200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-83600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-76800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-72100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-63000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-71400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-68900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-61900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-56300</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5948,8 +6122,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6037,8 +6214,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6126,8 +6306,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6215,83 +6398,86 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>185500</v>
+      </c>
+      <c r="E76" s="3">
         <v>186800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>189300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>193100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>159400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>166200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>160700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>157800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>120600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>116900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>110700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>107900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>85300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>81800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>82600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>90200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>84400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>90600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>69700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>78800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>70300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>72200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>18300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>23600</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6304,8 +6490,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6393,191 +6582,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45228</v>
+      </c>
+      <c r="E80" s="2">
         <v>45137</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44955</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44864</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44682</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44591</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44409</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44318</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44136</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44045</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43954</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43863</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43772</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43681</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43590</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43499</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43408</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43317</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43226</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43135</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43037</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42946</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42855</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42582</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>26200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>34200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>21700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>8400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-33700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6300</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6609,97 +6807,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E83" s="3">
         <v>3000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>800</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>700</v>
       </c>
       <c r="Z83" s="3">
         <v>700</v>
       </c>
       <c r="AA83" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB83" s="3">
         <v>800</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>300</v>
       </c>
       <c r="AC83" s="3">
         <v>300</v>
       </c>
       <c r="AD83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE83" s="3">
         <v>1200</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6787,8 +6989,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6876,8 +7081,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6965,8 +7173,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7054,8 +7265,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7143,97 +7357,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E89" s="3">
         <v>21100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>43800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-37600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-21800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>49200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-15900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>33600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>12600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>25200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-13400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-14900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>7200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>6800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-6300</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7265,97 +7485,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7443,8 +7667,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7532,97 +7759,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3100</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-1900</v>
       </c>
       <c r="O94" s="3">
         <v>-1900</v>
       </c>
       <c r="P94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>-2300</v>
       </c>
       <c r="AB94" s="3">
         <v>-2300</v>
       </c>
       <c r="AC94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7654,8 +7887,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7743,8 +7977,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7832,8 +8069,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7921,8 +8161,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8010,97 +8253,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-500</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-100</v>
       </c>
       <c r="G100" s="3">
         <v>-100</v>
       </c>
       <c r="H100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I100" s="3">
         <v>-1500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-900</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>25400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-300</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>57400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>7900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>6400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>5300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>8400</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8188,93 +8437,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E102" s="3">
         <v>9600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>39700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-13800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-46700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-28000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>44500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-20600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-12600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>30700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>9400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>20600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-16300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-13400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>46300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-7200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>700</v>
       </c>
-      <c r="AE102" s="3" t="s">
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
   <si>
     <t>LOVE</t>
   </si>
@@ -656,419 +656,432 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45326</v>
+      </c>
+      <c r="E7" s="2">
         <v>45228</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45137</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44955</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44864</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44682</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44591</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44409</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44318</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44136</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44045</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43954</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43863</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43772</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43681</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43590</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43499</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43408</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43317</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43226</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43135</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43037</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42946</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42855</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42582</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>250500</v>
+      </c>
+      <c r="E8" s="3">
         <v>154000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>154500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>141200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>238500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>134800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>148500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>129400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>196200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>116700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>102400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>82900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>129700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>74700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>61900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>54400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>92200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>52100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>48100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>41000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>64200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>41700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>33200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>26800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>39000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>24400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>20700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>17600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>30500</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>100900</v>
+      </c>
+      <c r="E9" s="3">
         <v>65600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>62100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>70600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>104800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>69900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>69400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>63400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>173600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>58100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>43400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>36800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>54600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>33400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>30900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>27100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>47000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>25800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>23900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>20000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>28700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>18800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>15400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>16100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>10700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>9200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>14700</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>149600</v>
+      </c>
+      <c r="E10" s="3">
         <v>88400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>92400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>70600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>133700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>64900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>79100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>66000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>22600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>58600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>59000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>46100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>75100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>41300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>31000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>27300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>45200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>26300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>24200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>21000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>35500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>22900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>17800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>14700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>22900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>13700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>11500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>9100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>15800</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1101,8 +1114,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1193,8 +1207,11 @@
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1285,8 +1302,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1311,24 +1331,24 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>-600</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>600</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1344,8 +1364,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1377,89 +1397,92 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E15" s="3">
         <v>3300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>700</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB15" s="3">
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC15" s="3">
         <v>800</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1469,8 +1492,11 @@
       <c r="AF15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1500,192 +1526,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>210100</v>
+      </c>
+      <c r="E17" s="3">
         <v>157600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>155500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>146900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>202000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>144900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>140400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>126900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>169900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>113700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>93400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>80700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>107900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>72200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>63000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>62800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>86800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>59000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>53100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>50300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>55900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>44400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>40200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>32400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>36500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>26500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>23100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>20800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>36500</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>40400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>36500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-10100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>8100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>26300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>21800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-6900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-9300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>8300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1718,50 +1751,51 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>800</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1769,13 +1803,13 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
       <c r="U20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V20" s="3">
         <v>200</v>
@@ -1787,10 +1821,10 @@
         <v>200</v>
       </c>
       <c r="Y20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="3">
         <v>-100</v>
@@ -1799,111 +1833,117 @@
         <v>-100</v>
       </c>
       <c r="AC20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>44600</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>2400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>39100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>28400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>23300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-8000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>9100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1989,144 +2029,150 @@
         <v>0</v>
       </c>
       <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
         <v>300</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>36500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>26300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>21700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-9100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-6300</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1000</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>10200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -2166,8 +2212,8 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
+      <c r="AC24" s="3">
+        <v>0</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
@@ -2178,8 +2224,11 @@
       <c r="AF24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2270,192 +2319,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>26200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>34200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>21700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-9100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>8400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-6300</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>26200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>34200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>21700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>8400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-33700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-6300</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2546,8 +2604,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2638,8 +2699,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2730,8 +2794,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2822,50 +2889,53 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2873,13 +2943,13 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
       <c r="U32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="V32" s="3">
         <v>-200</v>
@@ -2891,10 +2961,10 @@
         <v>-200</v>
       </c>
       <c r="Y32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="Z32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3">
         <v>100</v>
@@ -2903,111 +2973,117 @@
         <v>100</v>
       </c>
       <c r="AC32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>26200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>34200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>21700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>8400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-33700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-6300</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3098,197 +3174,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>26200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>34200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>21700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>8400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-33700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-6300</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45326</v>
+      </c>
+      <c r="E38" s="2">
         <v>45228</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45137</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44955</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44864</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44682</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44591</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44409</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44318</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44136</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44045</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43954</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43863</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43772</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43681</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43590</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43499</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43408</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43317</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43226</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43135</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43037</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42946</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42855</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42582</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3321,8 +3406,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3355,86 +3441,87 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E41" s="3">
         <v>37700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>54700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>45100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>43500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>17700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>64400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>92400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>47900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>68500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>65700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>78300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>47700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>54800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>45500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>48500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>27900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>44200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>35700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>49100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>44700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>48200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9200</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3447,8 +3534,11 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3539,86 +3629,89 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E43" s="3">
         <v>13000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>18400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2800</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3631,86 +3724,89 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>98400</v>
+      </c>
+      <c r="E44" s="3">
         <v>116600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>105000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>104500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>119600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>154500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>145700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>123000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>108500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>94500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>75000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>56000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>50400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>57800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>41000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>33400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>36400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>50200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>40700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>30900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>26200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>24600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>20200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>13900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>11600</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3723,86 +3819,89 @@
       <c r="AF44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E45" s="3">
         <v>16900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>15900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>15500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>35600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>31200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>11600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6300</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>5800</v>
       </c>
       <c r="Z45" s="3">
         <v>5800</v>
       </c>
       <c r="AA45" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AB45" s="3">
         <v>6100</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3815,86 +3914,89 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>214400</v>
+      </c>
+      <c r="E46" s="3">
         <v>184300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>183600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>181500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>187700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>209300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>203500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>206200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>221700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>163600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>161400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>140200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>143400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>123500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>107800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>91900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>100200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>95400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>97500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>78000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>85100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>78500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>78300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>24900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>29700</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3907,8 +4009,11 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3999,86 +4104,89 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>226700</v>
+      </c>
+      <c r="E48" s="3">
         <v>212300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>212400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>202800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>188300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>179500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>155300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>145400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>135000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>127700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>118400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>117600</v>
-      </c>
-      <c r="O48" s="3">
-        <v>25900</v>
       </c>
       <c r="P48" s="3">
         <v>25900</v>
       </c>
       <c r="Q48" s="3">
+        <v>25900</v>
+      </c>
+      <c r="R48" s="3">
         <v>25700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>24400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>23800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>18600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>17100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>15700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11000</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4091,8 +4199,11 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4106,13 +4217,13 @@
         <v>1600</v>
       </c>
       <c r="G49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H49" s="3">
         <v>3000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2900</v>
-      </c>
-      <c r="I49" s="3">
-        <v>3000</v>
       </c>
       <c r="J49" s="3">
         <v>3000</v>
@@ -4121,55 +4232,55 @@
         <v>3000</v>
       </c>
       <c r="L49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M49" s="3">
         <v>1500</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1300</v>
       </c>
       <c r="N49" s="3">
         <v>1300</v>
       </c>
       <c r="O49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P49" s="3">
         <v>1700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1200</v>
-      </c>
-      <c r="V49" s="3">
-        <v>1100</v>
       </c>
       <c r="W49" s="3">
         <v>1100</v>
       </c>
       <c r="X49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y49" s="3">
         <v>1000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>800</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>700</v>
       </c>
       <c r="AA49" s="3">
         <v>700</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>3</v>
+      <c r="AB49" s="3">
+        <v>700</v>
       </c>
       <c r="AC49" s="3" t="s">
         <v>3</v>
@@ -4183,8 +4294,11 @@
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4275,8 +4389,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4367,43 +4484,46 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E52" s="3">
         <v>38000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>36000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>35300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>31000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10800</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
       <c r="N52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
@@ -4415,13 +4535,13 @@
         <v>100</v>
       </c>
       <c r="R52" s="3">
+        <v>100</v>
+      </c>
+      <c r="S52" s="3">
         <v>200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>100</v>
-      </c>
-      <c r="T52" s="3">
-        <v>200</v>
       </c>
       <c r="U52" s="3">
         <v>200</v>
@@ -4436,16 +4556,16 @@
         <v>200</v>
       </c>
       <c r="Y52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Z52" s="3">
         <v>300</v>
       </c>
       <c r="AA52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>0</v>
       </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
@@ -4459,8 +4579,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4551,86 +4674,89 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>482200</v>
+      </c>
+      <c r="E54" s="3">
         <v>436300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>433600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>421200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>408600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>401100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>368900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>363600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>369100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>292800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>281300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>259200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>171000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>151100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>135300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>118100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>125700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>118700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>119300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>98800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>105000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>96800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>95100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>39100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>41400</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4643,8 +4769,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4677,8 +4806,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4711,86 +4841,87 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E57" s="3">
         <v>37200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>33900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>30100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>24600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>47300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>34200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>33200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>25400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>25900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>24300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>25200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>24500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>19900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>19000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>17700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>19800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>16800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>16900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>15300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12700</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4803,8 +4934,11 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4880,8 +5014,8 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
+      <c r="AB58" s="3">
+        <v>0</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
@@ -4895,86 +5029,89 @@
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>77500</v>
+      </c>
+      <c r="E59" s="3">
         <v>68700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>63500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>59000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>57500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>64100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>58600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>69600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>81400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>56100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>54700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>46000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>32000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>34300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>23600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4000</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4987,86 +5124,89 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>106400</v>
+      </c>
+      <c r="E60" s="3">
         <v>105900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>97300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>89100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>82000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>111400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>92900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>99400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>114700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>81600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>80600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>63700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>56300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>59500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>48000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>32300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>32400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>31800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>27100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>27400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>24600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>25100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>21500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>18200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>16700</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5079,8 +5219,11 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5151,11 +5294,11 @@
         <v>0</v>
       </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>1500</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5171,86 +5314,89 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>158300</v>
+      </c>
+      <c r="E62" s="3">
         <v>144900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>149400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>142800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>133500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>130200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>109900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>103500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>96600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>90700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>83700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>84700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1700</v>
-      </c>
-      <c r="V62" s="3">
-        <v>1600</v>
       </c>
       <c r="W62" s="3">
         <v>1600</v>
       </c>
       <c r="X62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Y62" s="3">
         <v>1400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1100</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5263,8 +5409,11 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5355,8 +5504,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5447,8 +5599,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5539,86 +5694,89 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>264700</v>
+      </c>
+      <c r="E66" s="3">
         <v>250800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>246800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>232000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>215500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>241600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>202700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>202900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>211300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>172200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>164300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>148500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>63100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>65900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>53500</v>
-      </c>
-      <c r="R66" s="3">
-        <v>35500</v>
       </c>
       <c r="S66" s="3">
         <v>35500</v>
       </c>
       <c r="T66" s="3">
+        <v>35500</v>
+      </c>
+      <c r="U66" s="3">
         <v>34300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>28700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>29000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>26200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>26500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>22900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>20800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>17800</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5631,8 +5789,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5665,8 +5826,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5757,8 +5919,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5849,8 +6014,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5941,8 +6109,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6033,86 +6204,89 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E72" s="3">
         <v>3400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-15700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-14200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-15900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-50200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-52900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-61400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-63400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-85100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-87600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-86500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-78200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-83600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-76800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-72100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-63000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-71400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-68900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-61900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-56300</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6125,8 +6299,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6217,8 +6394,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6309,8 +6489,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6401,86 +6584,89 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>217500</v>
+      </c>
+      <c r="E76" s="3">
         <v>185500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>186800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>189300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>193100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>159400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>166200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>160700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>157800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>120600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>116900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>110700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>107900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>85300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>81800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>82600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>90200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>84400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>90600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>69700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>78800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>70300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>72200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>18300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>23600</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6493,8 +6679,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6585,197 +6774,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45326</v>
+      </c>
+      <c r="E80" s="2">
         <v>45228</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45137</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44955</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44864</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44682</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44591</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44409</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44318</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44136</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44045</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43954</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43863</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43772</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43681</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43590</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43499</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43408</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43317</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43226</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43135</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43037</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42946</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42855</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42582</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>26200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>34200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>21700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>8400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-33700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-6300</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6808,100 +7006,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E83" s="3">
         <v>3300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>800</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>700</v>
       </c>
       <c r="AA83" s="3">
         <v>700</v>
       </c>
       <c r="AB83" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC83" s="3">
         <v>800</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>300</v>
       </c>
       <c r="AD83" s="3">
         <v>300</v>
       </c>
       <c r="AE83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF83" s="3">
         <v>1200</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6992,8 +7194,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7084,8 +7289,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7176,8 +7384,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7268,8 +7479,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7360,100 +7574,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>21100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>43800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-37600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-21800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>49200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-15900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>33600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>12600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>25200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-13400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-14900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-8200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>7200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>6800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-6300</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7486,100 +7706,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7670,8 +7894,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7762,100 +7989,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3100</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-1900</v>
       </c>
       <c r="P94" s="3">
         <v>-1900</v>
       </c>
       <c r="Q94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="R94" s="3">
         <v>-2900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>-2300</v>
       </c>
       <c r="AC94" s="3">
         <v>-2300</v>
       </c>
       <c r="AD94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7888,8 +8121,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7980,8 +8214,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8072,8 +8309,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8164,8 +8404,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8256,8 +8499,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8265,91 +8511,94 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-3100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-500</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-100</v>
       </c>
       <c r="H100" s="3">
         <v>-100</v>
       </c>
       <c r="I100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J100" s="3">
         <v>-1500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-900</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>25400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-300</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>57400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>7900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>6400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>5300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>8400</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8440,96 +8689,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>49300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>39700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-13800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-46700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-28000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>44500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-20600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>30700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>9400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>20600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-16300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>8500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-13400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>46300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-7200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>4900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>700</v>
       </c>
-      <c r="AF102" s="3" t="s">
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
   <si>
     <t>LOVE</t>
   </si>
@@ -656,432 +656,458 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45508</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45417</v>
+      </c>
+      <c r="F7" s="2">
         <v>45326</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45228</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45137</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44955</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44864</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44682</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44591</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44409</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44318</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44136</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44045</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43954</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43863</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43772</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43681</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43590</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43499</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43408</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43317</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43226</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43135</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43037</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42946</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42855</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42582</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>156600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>132600</v>
+      </c>
+      <c r="F8" s="3">
         <v>250500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>154000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>154500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>141200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>238500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>134800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>148500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>129400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>196200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>116700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>102400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>82900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>129700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>74700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>61900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>54400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>92200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>52100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>48100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>41000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>64200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>41700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>33200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>26800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>39000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>24400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>20700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>17600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>30500</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>64200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>60600</v>
+      </c>
+      <c r="F9" s="3">
         <v>100900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>65600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>62100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>70600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>104800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>69900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>69400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>63400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>173600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>58100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>43400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>36800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>54600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>33400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>30900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>27100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>47000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>25800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>23900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>20000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>28700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>18800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>15400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>12100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>16100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>10700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>9200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>8500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>14700</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>92400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>72000</v>
+      </c>
+      <c r="F10" s="3">
         <v>149600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>88400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>92400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>70600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>133700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>64900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>79100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>66000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>22600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>58600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>59000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>46100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>75100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>41300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>31000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>27300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>45200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>26300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>24200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>21000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>35500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>22900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>17800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>14700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>22900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>13700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>11500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>9100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>15800</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1115,8 +1141,10 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1210,8 +1238,14 @@
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1305,8 +1339,14 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1334,27 +1374,27 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>-600</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1367,11 +1407,11 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1400,103 +1440,115 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E15" s="3">
         <v>3500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G15" s="3">
         <v>3300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>3000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>5600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>2600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>4900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>3100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>5300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>4200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>1700</v>
-      </c>
-      <c r="N15" s="3">
-        <v>1600</v>
-      </c>
-      <c r="O15" s="3">
-        <v>2400</v>
       </c>
       <c r="P15" s="3">
         <v>1600</v>
       </c>
       <c r="Q15" s="3">
+        <v>2400</v>
+      </c>
+      <c r="R15" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S15" s="3">
         <v>1900</v>
-      </c>
-      <c r="R15" s="3">
-        <v>1500</v>
-      </c>
-      <c r="S15" s="3">
-        <v>1600</v>
       </c>
       <c r="T15" s="3">
         <v>1500</v>
       </c>
       <c r="U15" s="3">
+        <v>1600</v>
+      </c>
+      <c r="V15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="W15" s="3">
         <v>1400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>1200</v>
-      </c>
-      <c r="W15" s="3">
-        <v>1100</v>
-      </c>
-      <c r="X15" s="3">
-        <v>600</v>
       </c>
       <c r="Y15" s="3">
         <v>1100</v>
       </c>
       <c r="Z15" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB15" s="3">
         <v>800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>700</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE15" s="3">
         <v>800</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1527,198 +1579,212 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>150500</v>
+      </c>
+      <c r="F17" s="3">
         <v>210100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>157600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>155500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>146900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>202000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>144900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>140400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>126900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>169900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>113700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>93400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>80700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>107900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>72200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>63000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>62800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>86800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>59000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>53100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>50300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>55900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>44400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>40200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>32400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>36500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>26500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>23100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>20800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>36500</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="F18" s="3">
         <v>40400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-3600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-5700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>36500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-10100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>8100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>2500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>26300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>3000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>9000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>2200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>21800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>2500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-8400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>5400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-6900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-5000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-9300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>8300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>2500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1752,28 +1818,30 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
         <v>800</v>
       </c>
-      <c r="E20" s="3">
-        <v>300</v>
-      </c>
       <c r="F20" s="3">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="G20" s="3">
         <v>300</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I20" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1791,31 +1859,31 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
-      </c>
-      <c r="V20" s="3">
-        <v>200</v>
-      </c>
-      <c r="W20" s="3">
-        <v>200</v>
       </c>
       <c r="X20" s="3">
         <v>200</v>
@@ -1824,19 +1892,19 @@
         <v>200</v>
       </c>
       <c r="Z20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AA20" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="AB20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="3">
         <v>-100</v>
       </c>
       <c r="AD20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE20" s="3">
         <v>-100</v>
@@ -1844,106 +1912,118 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="F21" s="3">
         <v>44600</v>
       </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>2400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-2500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>39100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-7700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>11200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>5100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>28400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>4700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>10600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>4600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>23300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>4300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-6700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>6900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-5400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-3600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-8000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>9100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>3100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2032,152 +2112,164 @@
         <v>0</v>
       </c>
       <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
         <v>300</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="F23" s="3">
         <v>41200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-3300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-5400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>36500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-10200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>8100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>26300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>2900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>9000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>2200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>21700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>2500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-8300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>5400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-6700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-4800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-9100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>8500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>2500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-6300</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F24" s="3">
         <v>10200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-1000</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-1300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>10200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-2800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>2300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-7900</v>
-      </c>
-      <c r="M24" s="3">
-        <v>200</v>
-      </c>
-      <c r="N24" s="3">
-        <v>500</v>
       </c>
       <c r="O24" s="3">
         <v>200</v>
       </c>
       <c r="P24" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Q24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2215,11 +2307,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE24" s="3" t="s">
-        <v>3</v>
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>0</v>
       </c>
       <c r="AF24" s="3" t="s">
         <v>3</v>
@@ -2227,8 +2319,14 @@
       <c r="AG24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2322,198 +2420,216 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="F26" s="3">
         <v>31000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-4100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>26200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-7400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>5800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>34200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>2800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>8400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>21700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>2500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-8300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>5400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-6700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-4800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-9100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>8400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>2400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-6300</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="F27" s="3">
         <v>31000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-4100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>26200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-7400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>5800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>34200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>2800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>8400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>21700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>2500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-8300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>5400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-6700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-4800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-9100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>8400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-33700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>1900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-6300</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2607,8 +2723,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2702,8 +2824,14 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2797,8 +2925,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2892,28 +3026,34 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-800</v>
       </c>
-      <c r="E32" s="3">
-        <v>-300</v>
-      </c>
       <c r="F32" s="3">
-        <v>-400</v>
+        <v>-800</v>
       </c>
       <c r="G32" s="3">
         <v>-300</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="I32" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -2931,31 +3071,31 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-200</v>
       </c>
       <c r="X32" s="3">
         <v>-200</v>
@@ -2964,19 +3104,19 @@
         <v>-200</v>
       </c>
       <c r="Z32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AA32" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="AB32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC32" s="3">
         <v>100</v>
       </c>
       <c r="AD32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE32" s="3">
         <v>100</v>
@@ -2984,106 +3124,118 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="F33" s="3">
         <v>31000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-4100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>26200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-7400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>5800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>34200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>2800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>8400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>2100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>21700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>2500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-8300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>5400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-6700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-4800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-9100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>8400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-33700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>1900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-6300</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3177,203 +3329,221 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="F35" s="3">
         <v>31000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-4100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>26200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-7400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>5800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>34200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>2800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>8400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>2100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>21700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>2500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-8300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>5400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-6700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-4800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-9100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>8400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-33700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>1900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-6300</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45508</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45417</v>
+      </c>
+      <c r="F38" s="2">
         <v>45326</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45228</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45137</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44955</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44864</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44682</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44591</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44409</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44318</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44136</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44045</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43954</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43863</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43772</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43681</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43590</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43499</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43408</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43317</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43226</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43135</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43037</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42946</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42855</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42582</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3407,8 +3577,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3442,92 +3614,94 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>72100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>72400</v>
+      </c>
+      <c r="F41" s="3">
         <v>87000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>37700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>54700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>45100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>43500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>17700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>64400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>92400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>47900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>68500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>65700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>78300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>47700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>54800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>45500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>48500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>27900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>44200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>35700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>49100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>44700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>48200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>9200</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3537,8 +3711,14 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3632,92 +3812,98 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F43" s="3">
         <v>13500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>13000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>8000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>18400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>9100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>15400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>9000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>6400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>8500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>9800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>7400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>6900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>7200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>6200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>7100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>7200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>8600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>5600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>5000</v>
-      </c>
-      <c r="X43" s="3">
-        <v>4000</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>2900</v>
       </c>
       <c r="Z43" s="3">
         <v>4000</v>
       </c>
       <c r="AA43" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AB43" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AC43" s="3">
         <v>3400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>2800</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3727,92 +3913,98 @@
       <c r="AG43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>88300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>94700</v>
+      </c>
+      <c r="F44" s="3">
         <v>98400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>116600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>105000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>104500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>119600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>154500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>145700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>123000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>108500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>94500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>75000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>56000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>50400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>57800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>41000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>33400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>36400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>50200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>40700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>30900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>26200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>24600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>20200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>13900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>11600</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3822,92 +4014,98 @@
       <c r="AG44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>16500</v>
+      </c>
+      <c r="F45" s="3">
         <v>15500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>16900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>15900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>13400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>15500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>35600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>31200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>12400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>12300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>11400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>10600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>11600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>10100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>10900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>5700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>5900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>8100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>8700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>7000</v>
-      </c>
-      <c r="W45" s="3">
-        <v>6300</v>
-      </c>
-      <c r="X45" s="3">
-        <v>5900</v>
       </c>
       <c r="Y45" s="3">
         <v>6300</v>
       </c>
       <c r="Z45" s="3">
+        <v>5900</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AB45" s="3">
         <v>5800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>5800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>6100</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3917,92 +4115,98 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>194200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>190800</v>
+      </c>
+      <c r="F46" s="3">
         <v>214400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>184300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>183600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>181500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>187700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>209300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>203500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>206200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>221700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>163600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>161400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>140200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>143400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>123500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>107800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>91900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>100200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>95400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>97500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>78000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>85100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>78500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>78300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>24900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>29700</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4012,8 +4216,14 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4107,92 +4317,98 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>236100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>239500</v>
+      </c>
+      <c r="F48" s="3">
         <v>226700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>212300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>212400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>202800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>188300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>179500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>155300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>145400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>135000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>127700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>118400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>117600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>25900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>25900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>25700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>24400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>23800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>21800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>20400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>19500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>18600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>17100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>15700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>13200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>11000</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4202,8 +4418,14 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4220,34 +4442,34 @@
         <v>1600</v>
       </c>
       <c r="H49" s="3">
-        <v>3000</v>
+        <v>1600</v>
       </c>
       <c r="I49" s="3">
-        <v>2900</v>
+        <v>1600</v>
       </c>
       <c r="J49" s="3">
         <v>3000</v>
       </c>
       <c r="K49" s="3">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="L49" s="3">
         <v>3000</v>
       </c>
       <c r="M49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O49" s="3">
         <v>1500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1300</v>
-      </c>
-      <c r="P49" s="3">
-        <v>1700</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>1600</v>
       </c>
       <c r="R49" s="3">
         <v>1700</v>
@@ -4256,38 +4478,38 @@
         <v>1600</v>
       </c>
       <c r="T49" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="V49" s="3">
         <v>1500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>1100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>700</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4297,8 +4519,14 @@
       <c r="AG49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4392,8 +4620,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4487,49 +4721,55 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>49200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>45300</v>
+      </c>
+      <c r="F52" s="3">
         <v>39500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>38000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>36000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>35300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>31000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>10800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>8600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>10400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>10800</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
       <c r="O52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
@@ -4538,7 +4778,7 @@
         <v>100</v>
       </c>
       <c r="S52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T52" s="3">
         <v>100</v>
@@ -4547,7 +4787,7 @@
         <v>200</v>
       </c>
       <c r="V52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W52" s="3">
         <v>200</v>
@@ -4559,19 +4799,19 @@
         <v>200</v>
       </c>
       <c r="Z52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB52" s="3">
         <v>300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>300</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD52" s="3" t="s">
-        <v>3</v>
+      <c r="AD52" s="3">
+        <v>0</v>
       </c>
       <c r="AE52" s="3" t="s">
         <v>3</v>
@@ -4582,8 +4822,14 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4677,92 +4923,98 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>481100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>477200</v>
+      </c>
+      <c r="F54" s="3">
         <v>482200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>436300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>433600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>421200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>408600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>401100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>368900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>363600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>369100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>292800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>281300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>259200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>171000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>151100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>135300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>118100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>125700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>118700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>119300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>98800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>105000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>96800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>95100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>39100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>41400</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4772,8 +5024,14 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4807,8 +5065,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4842,92 +5102,94 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>28100</v>
+      </c>
+      <c r="F57" s="3">
         <v>28800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>37200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>33900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>30100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>24600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>47300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>34200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>29800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>33200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>25400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>25900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>17700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>24300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>25200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>24500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>17400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>19900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>19000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>17700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>19800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>16800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>16900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>15300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>12200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>12700</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4937,8 +5199,14 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5017,11 +5285,11 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD58" s="3" t="s">
-        <v>3</v>
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>0</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>3</v>
@@ -5032,92 +5300,98 @@
       <c r="AG58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>86600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>77400</v>
+      </c>
+      <c r="F59" s="3">
         <v>77500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>68700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>63500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>59000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>57500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>64100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>58600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>69600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>81400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>56100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>54700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>46000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>32000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>34300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>23600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>14900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>12500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>12800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>9400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>7700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>7800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>8200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>6200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>5900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>4000</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5127,92 +5401,98 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>115100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>105500</v>
+      </c>
+      <c r="F60" s="3">
         <v>106400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>105900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>97300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>89100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>82000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>111400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>92900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>99400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>114700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>81600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>80600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>63700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>56300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>59500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>48000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>32300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>32400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>31800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>27100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>27400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>24600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>25100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>21500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>18200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>16700</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5222,8 +5502,14 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5297,14 +5583,14 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>1500</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5317,92 +5603,98 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>163900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>166300</v>
+      </c>
+      <c r="F62" s="3">
         <v>158300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>144900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>149400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>142800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>133500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>130200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>109900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>103500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>96600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>90700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>83700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>84700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>6700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>6400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>5500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>3100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1100</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5412,8 +5704,14 @@
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5507,8 +5805,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5602,8 +5906,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5697,92 +6007,98 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>278900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>271900</v>
+      </c>
+      <c r="F66" s="3">
         <v>264700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>250800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>246800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>232000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>215500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>241600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>202700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>202900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>211300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>172200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>164300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>148500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>63100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>65900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>53500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>35500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>35500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>34300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>28700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>29000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>26200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>26500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>22900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>20800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>17800</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5792,8 +6108,14 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5827,8 +6149,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5922,8 +6246,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6017,8 +6347,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6112,8 +6448,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6207,92 +6549,98 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>21400</v>
+      </c>
+      <c r="F72" s="3">
         <v>34400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>3400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>5800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>6400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>10500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-15700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-8300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-14200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-15900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-50200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-52900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-61400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-63400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-85100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-87600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-86500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-78200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-83600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-76800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-72100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-63000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-71400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-68900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-61900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-56300</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6302,8 +6650,14 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6397,8 +6751,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6492,8 +6852,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6587,92 +6953,98 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>202100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>205300</v>
+      </c>
+      <c r="F76" s="3">
         <v>217500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>185500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>186800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>189300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>193100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>159400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>166200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>160700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>157800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>120600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>116900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>110700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>107900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>85300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>81800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>82600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>90200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>84400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>90600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>69700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>78800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>70300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>72200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>18300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>23600</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6682,8 +7054,14 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6777,203 +7155,221 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45508</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45417</v>
+      </c>
+      <c r="F80" s="2">
         <v>45326</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45228</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45137</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44955</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44864</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44682</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44591</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44409</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44318</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44136</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44045</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43954</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43863</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43772</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43681</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43590</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43499</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43408</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43317</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43226</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43135</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43037</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42946</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42855</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42582</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="F81" s="3">
         <v>31000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-4100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>26200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-7400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>5800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>34200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>2800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>8400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>2100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>21700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>2500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-8300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>5400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-6700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-4800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-9100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>8400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-33700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>1900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-6300</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7007,103 +7403,111 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E83" s="3">
         <v>3500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G83" s="3">
         <v>3300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>3000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>2800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>2600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>2500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>3100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>2700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>2100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1700</v>
-      </c>
-      <c r="N83" s="3">
-        <v>1600</v>
-      </c>
-      <c r="O83" s="3">
-        <v>2400</v>
       </c>
       <c r="P83" s="3">
         <v>1600</v>
       </c>
       <c r="Q83" s="3">
+        <v>2400</v>
+      </c>
+      <c r="R83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S83" s="3">
         <v>1900</v>
-      </c>
-      <c r="R83" s="3">
-        <v>1500</v>
-      </c>
-      <c r="S83" s="3">
-        <v>1600</v>
       </c>
       <c r="T83" s="3">
         <v>1500</v>
       </c>
       <c r="U83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="V83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="W83" s="3">
         <v>1400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>1200</v>
-      </c>
-      <c r="W83" s="3">
-        <v>1100</v>
-      </c>
-      <c r="X83" s="3">
-        <v>600</v>
       </c>
       <c r="Y83" s="3">
         <v>1100</v>
       </c>
       <c r="Z83" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB83" s="3">
         <v>800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>1200</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7197,8 +7601,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7292,8 +7702,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7387,8 +7803,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7482,8 +7904,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7577,103 +8005,115 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F89" s="3">
         <v>56300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-7200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>21100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>6300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>43800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-5800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-37600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-21800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>49200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-15900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>10400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-9600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>33600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-5100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>12600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>25200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-13400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-14900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-8200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>7200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>6800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-6300</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7707,103 +8147,111 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-7000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-9700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-8300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-4200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-7200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-8200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-5600</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-3300</v>
       </c>
       <c r="M91" s="3">
         <v>-4500</v>
       </c>
       <c r="N91" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="P91" s="3">
         <v>-4300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-2900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-1800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-2800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-2100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-3400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-2700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-2200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-1900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7897,8 +8345,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7992,103 +8446,115 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-7000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-9700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-8300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-4200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-7200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-8200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-5600</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-3300</v>
       </c>
       <c r="M94" s="3">
         <v>-4500</v>
       </c>
       <c r="N94" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="O94" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="P94" s="3">
         <v>-4300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-3100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-2900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-2300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-3700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-2900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-2100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-2000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8122,8 +8588,10 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8217,8 +8685,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8312,8 +8786,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8407,8 +8887,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8502,103 +8988,115 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-3100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1500</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
       </c>
       <c r="M100" s="3">
         <v>-200</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P100" s="3">
         <v>-3300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-900</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>25400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-3200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-300</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>57400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>1200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>7900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>6400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>5300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>8400</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8692,99 +9190,111 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="F102" s="3">
         <v>49300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-17000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>9600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>39700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-13800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-46700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-28000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>44500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-20600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>2700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-12600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>30700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-7100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>9400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-3100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>20600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-16300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>8500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-13400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>4400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>46300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-7200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>3500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>4900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>700</v>
       </c>
-      <c r="AG102" s="3" t="s">
+      <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
   <si>
     <t>LOVE</t>
   </si>
@@ -1467,7 +1467,7 @@
         <v>3000</v>
       </c>
       <c r="I15" s="3">
-        <v>5600</v>
+        <v>2800</v>
       </c>
       <c r="J15" s="3">
         <v>2600</v>
@@ -1825,26 +1825,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>700</v>
-      </c>
-      <c r="E20" s="3">
-        <v>800</v>
-      </c>
-      <c r="F20" s="3">
-        <v>800</v>
-      </c>
-      <c r="G20" s="3">
-        <v>300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>400</v>
-      </c>
-      <c r="I20" s="3">
-        <v>300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>-100</v>
@@ -1927,22 +1927,22 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-3900</v>
+        <v>-4600</v>
       </c>
       <c r="E21" s="3">
-        <v>-13600</v>
+        <v>-14400</v>
       </c>
       <c r="F21" s="3">
-        <v>44600</v>
+        <v>43800</v>
       </c>
       <c r="G21" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="H21" s="3">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="I21" s="3">
-        <v>-2500</v>
+        <v>-2900</v>
       </c>
       <c r="J21" s="3">
         <v>39100</v>
@@ -2027,23 +2027,23 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -3037,26 +3037,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>100</v>
@@ -4026,25 +4026,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>19000</v>
+        <v>3700</v>
       </c>
       <c r="E45" s="3">
-        <v>16500</v>
+        <v>2000</v>
       </c>
       <c r="F45" s="3">
-        <v>15500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>16900</v>
-      </c>
-      <c r="H45" s="3">
-        <v>15900</v>
-      </c>
-      <c r="I45" s="3">
-        <v>13400</v>
+        <v>3800</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J45" s="3">
-        <v>15500</v>
+        <v>5100</v>
       </c>
       <c r="K45" s="3">
         <v>35600</v>
@@ -4227,26 +4227,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4448,7 +4448,7 @@
         <v>1600</v>
       </c>
       <c r="J49" s="3">
-        <v>3000</v>
+        <v>1600</v>
       </c>
       <c r="K49" s="3">
         <v>2900</v>
@@ -4733,25 +4733,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>49200</v>
+        <v>32300</v>
       </c>
       <c r="E52" s="3">
-        <v>45300</v>
+        <v>30400</v>
       </c>
       <c r="F52" s="3">
-        <v>39500</v>
+        <v>28700</v>
       </c>
       <c r="G52" s="3">
-        <v>38000</v>
+        <v>26900</v>
       </c>
       <c r="H52" s="3">
-        <v>36000</v>
+        <v>25900</v>
       </c>
       <c r="I52" s="3">
-        <v>35300</v>
+        <v>25400</v>
       </c>
       <c r="J52" s="3">
-        <v>31000</v>
+        <v>22400</v>
       </c>
       <c r="K52" s="3">
         <v>10800</v>
@@ -5211,25 +5211,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>18500</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>17600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>16100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>16900</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>13100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5312,25 +5312,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>86600</v>
+        <v>20100</v>
       </c>
       <c r="E59" s="3">
-        <v>77400</v>
+        <v>14600</v>
       </c>
       <c r="F59" s="3">
-        <v>77500</v>
+        <v>22900</v>
       </c>
       <c r="G59" s="3">
-        <v>68700</v>
+        <v>12700</v>
       </c>
       <c r="H59" s="3">
-        <v>63500</v>
+        <v>15400</v>
       </c>
       <c r="I59" s="3">
-        <v>59000</v>
+        <v>17500</v>
       </c>
       <c r="J59" s="3">
-        <v>57500</v>
+        <v>12700</v>
       </c>
       <c r="K59" s="3">
         <v>64100</v>
@@ -5514,25 +5514,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>163400</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>165900</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>157900</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>144900</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>149400</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>142800</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>133500</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5615,25 +5615,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>163900</v>
+        <v>500</v>
       </c>
       <c r="E62" s="3">
-        <v>166300</v>
+        <v>500</v>
       </c>
       <c r="F62" s="3">
-        <v>158300</v>
-      </c>
-      <c r="G62" s="3">
-        <v>144900</v>
-      </c>
-      <c r="H62" s="3">
-        <v>149400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>142800</v>
-      </c>
-      <c r="J62" s="3">
-        <v>133500</v>
+        <v>500</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>130200</v>
@@ -7411,25 +7411,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3800</v>
+        <v>2900</v>
       </c>
       <c r="E83" s="3">
-        <v>3500</v>
+        <v>2700</v>
       </c>
       <c r="F83" s="3">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="G83" s="3">
-        <v>3300</v>
+        <v>2400</v>
       </c>
       <c r="H83" s="3">
         <v>3000</v>
       </c>
       <c r="I83" s="3">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="J83" s="3">
-        <v>2600</v>
+        <v>2000</v>
       </c>
       <c r="K83" s="3">
         <v>2500</v>
@@ -8035,7 +8035,7 @@
         <v>6300</v>
       </c>
       <c r="J89" s="3">
-        <v>43800</v>
+        <v>47000</v>
       </c>
       <c r="K89" s="3">
         <v>-5800</v>
@@ -8155,25 +8155,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-6200</v>
+        <v>-6100</v>
       </c>
       <c r="E91" s="3">
         <v>-7300</v>
       </c>
       <c r="F91" s="3">
-        <v>-7000</v>
+        <v>-6800</v>
       </c>
       <c r="G91" s="3">
-        <v>-9700</v>
+        <v>-9600</v>
       </c>
       <c r="H91" s="3">
-        <v>-8300</v>
+        <v>-8200</v>
       </c>
       <c r="I91" s="3">
         <v>-4200</v>
       </c>
       <c r="J91" s="3">
-        <v>-7200</v>
+        <v>-7100</v>
       </c>
       <c r="K91" s="3">
         <v>-8200</v>
@@ -8595,26 +8595,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -9100,26 +9100,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
   <si>
     <t>LOVE</t>
   </si>
@@ -656,458 +656,470 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45599</v>
+      </c>
+      <c r="E7" s="2">
         <v>45508</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45417</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45326</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45228</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45137</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44955</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44864</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44682</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44591</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44409</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44318</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44227</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44136</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44045</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43954</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43863</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43772</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43681</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43590</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43499</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43408</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43317</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43226</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43135</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43037</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42946</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42855</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42582</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="AJ7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>149900</v>
+      </c>
+      <c r="E8" s="3">
         <v>156600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>132600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>250500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>154000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>154500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>141200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>238500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>134800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>148500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>129400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>196200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>116700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>102400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>82900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>129700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>74700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>61900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>54400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>92200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>52100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>48100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>41000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>64200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>41700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>33200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>26800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>39000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>24400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>20700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>17600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>30500</v>
       </c>
-      <c r="AI8" s="3" t="s">
+      <c r="AJ8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>62300</v>
+      </c>
+      <c r="E9" s="3">
         <v>64200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>60600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>100900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>65600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>62100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>70600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>104800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>69900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>69400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>63400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>173600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>58100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>43400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>36800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>54600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>33400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>30900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>27100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>47000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>25800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>23900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>20000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>28700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>18800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>15400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>12100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>16100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>10700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>9200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>14700</v>
       </c>
-      <c r="AI9" s="3" t="s">
+      <c r="AJ9" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>87600</v>
+      </c>
+      <c r="E10" s="3">
         <v>92400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>72000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>149600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>88400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>92400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>70600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>133700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>64900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>79100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>66000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>22600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>58600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>59000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>46100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>75100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>41300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>31000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>27300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>45200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>26300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>24200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>21000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>35500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>22900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>17800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>14700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>22900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>13700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>11500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>9100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>15800</v>
       </c>
-      <c r="AI10" s="3" t="s">
+      <c r="AJ10" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1143,8 +1155,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1244,8 +1257,11 @@
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1345,8 +1361,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1380,24 +1399,24 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>-600</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>600</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
         <v>200</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1413,8 +1432,8 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1446,98 +1465,101 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E15" s="3">
         <v>3800</v>
-      </c>
-      <c r="E15" s="3">
-        <v>3500</v>
       </c>
       <c r="F15" s="3">
         <v>3500</v>
       </c>
       <c r="G15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H15" s="3">
         <v>3300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>700</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF15" s="3">
         <v>800</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1547,8 +1569,11 @@
       <c r="AI15" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ15" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1581,210 +1606,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>157600</v>
+      </c>
+      <c r="E17" s="3">
         <v>165000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>150500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>210100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>157600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>155500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>146900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>202000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>144900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>140400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>126900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>169900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>113700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>93400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>80700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>107900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>72200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>63000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>62800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>86800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>59000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>53100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>50300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>55900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>44400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>40200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>32400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>36500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>26500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>23100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>20800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>36500</v>
       </c>
-      <c r="AI17" s="3" t="s">
+      <c r="AJ17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-17900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>40400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>36500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>26300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>21800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-6900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>8300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-5600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI18" s="3" t="s">
+      <c r="AJ18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1820,8 +1852,9 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1846,33 +1879,33 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1880,13 +1913,13 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3">
         <v>100</v>
       </c>
       <c r="X20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y20" s="3">
         <v>200</v>
@@ -1898,10 +1931,10 @@
         <v>200</v>
       </c>
       <c r="AB20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AC20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="3">
         <v>-100</v>
@@ -1910,120 +1943,126 @@
         <v>-100</v>
       </c>
       <c r="AF20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-100</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="3" t="s">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-14400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>43800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>39100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>28400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>23300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-6700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-5400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AI21" s="3" t="s">
+      <c r="AJ21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2045,8 +2084,8 @@
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2118,162 +2157,168 @@
         <v>0</v>
       </c>
       <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
         <v>300</v>
       </c>
-      <c r="AI22" s="3" t="s">
+      <c r="AJ22" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-17100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>41200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>36500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>26300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>9000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>21700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-6300</v>
       </c>
-      <c r="AI23" s="3" t="s">
+      <c r="AJ23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-4200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1000</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-1300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>10200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-7900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -2313,8 +2358,8 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>3</v>
+      <c r="AF24" s="3">
+        <v>0</v>
       </c>
       <c r="AG24" s="3" t="s">
         <v>3</v>
@@ -2325,8 +2370,11 @@
       <c r="AI24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2426,210 +2474,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>31000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>26200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>34200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>8400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>21700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>8400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-6300</v>
       </c>
-      <c r="AI26" s="3" t="s">
+      <c r="AJ26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>31000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>26200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>34200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>8400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>21700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>8400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-33700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-6400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-6300</v>
       </c>
-      <c r="AI27" s="3" t="s">
+      <c r="AJ27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2729,8 +2786,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2830,8 +2890,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2931,8 +2994,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3032,8 +3098,11 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3058,33 +3127,33 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -3092,13 +3161,13 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W32" s="3">
         <v>-100</v>
       </c>
       <c r="X32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Y32" s="3">
         <v>-200</v>
@@ -3110,10 +3179,10 @@
         <v>-200</v>
       </c>
       <c r="AB32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AC32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD32" s="3">
         <v>100</v>
@@ -3122,120 +3191,126 @@
         <v>100</v>
       </c>
       <c r="AF32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>100</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="3" t="s">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>31000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>26200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>34200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>8400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>21700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>8400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-33700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-6400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-6300</v>
       </c>
-      <c r="AI33" s="3" t="s">
+      <c r="AJ33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3335,215 +3410,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>31000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>26200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>34200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>8400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>21700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>8400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-33700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-6400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-6300</v>
       </c>
-      <c r="AI35" s="3" t="s">
+      <c r="AJ35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45599</v>
+      </c>
+      <c r="E38" s="2">
         <v>45508</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45417</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45326</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45228</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45137</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44955</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44864</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44682</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44591</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44409</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44318</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44227</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44136</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44045</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43954</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43863</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43772</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43681</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43590</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43499</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43408</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43317</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43226</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43135</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43037</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42946</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42855</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42582</v>
       </c>
-      <c r="AI38" s="2" t="s">
+      <c r="AJ38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3579,8 +3663,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3616,95 +3701,96 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>61700</v>
+      </c>
+      <c r="E41" s="3">
         <v>72100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>72400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>87000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>37700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>54700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>45100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>43500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>64400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>92400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>47900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>68500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>65700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>78300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>47700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>54800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>45500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>48500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>27900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>44200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>35700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>49100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>44700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>48200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>9200</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3717,8 +3803,11 @@
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3818,95 +3907,98 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E43" s="3">
         <v>14800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>18400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>8600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2800</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3919,95 +4011,98 @@
       <c r="AI43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>113400</v>
+      </c>
+      <c r="E44" s="3">
         <v>88300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>94700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>98400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>116600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>105000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>104500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>119600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>154500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>145700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>123000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>108500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>94500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>75000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>56000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>50400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>57800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>41000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>33400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>36400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>50200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>40700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>30900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>26200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>24600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>20200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>13900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>11600</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4020,95 +4115,98 @@
       <c r="AI44" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ44" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3800</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>5100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>35600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>31200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>11600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6300</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>5800</v>
       </c>
       <c r="AC45" s="3">
         <v>5800</v>
       </c>
       <c r="AD45" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AE45" s="3">
         <v>6100</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4121,95 +4219,98 @@
       <c r="AI45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>209900</v>
+      </c>
+      <c r="E46" s="3">
         <v>194200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>190800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>214400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>184300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>183600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>181500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>187700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>209300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>203500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>206200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>221700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>163600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>161400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>140200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>143400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>123500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>107800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>91900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>100200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>95400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>97500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>78000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>85100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>78500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>78300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>24900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>29700</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4222,8 +4323,11 @@
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4248,8 +4352,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4323,95 +4427,98 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>234900</v>
+      </c>
+      <c r="E48" s="3">
         <v>236100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>239500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>226700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>212300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>212400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>202800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>188300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>179500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>155300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>145400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>135000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>127700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>118400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>117600</v>
-      </c>
-      <c r="R48" s="3">
-        <v>25900</v>
       </c>
       <c r="S48" s="3">
         <v>25900</v>
       </c>
       <c r="T48" s="3">
+        <v>25900</v>
+      </c>
+      <c r="U48" s="3">
         <v>25700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>24400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>23800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>18600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>17100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>15700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11000</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4424,13 +4531,16 @@
       <c r="AI48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="E49" s="3">
         <v>1600</v>
@@ -4451,10 +4561,10 @@
         <v>1600</v>
       </c>
       <c r="K49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L49" s="3">
         <v>2900</v>
-      </c>
-      <c r="L49" s="3">
-        <v>3000</v>
       </c>
       <c r="M49" s="3">
         <v>3000</v>
@@ -4463,55 +4573,55 @@
         <v>3000</v>
       </c>
       <c r="O49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P49" s="3">
         <v>1500</v>
-      </c>
-      <c r="P49" s="3">
-        <v>1300</v>
       </c>
       <c r="Q49" s="3">
         <v>1300</v>
       </c>
       <c r="R49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S49" s="3">
         <v>1700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>1100</v>
       </c>
       <c r="Z49" s="3">
         <v>1100</v>
       </c>
       <c r="AA49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB49" s="3">
         <v>1000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>800</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>700</v>
       </c>
       <c r="AD49" s="3">
         <v>700</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>3</v>
+      <c r="AE49" s="3">
+        <v>700</v>
       </c>
       <c r="AF49" s="3" t="s">
         <v>3</v>
@@ -4525,8 +4635,11 @@
       <c r="AI49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4626,8 +4739,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4727,52 +4843,55 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E52" s="3">
         <v>32300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>30400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>28700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>26900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>25900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>25400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>22400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10800</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
       <c r="Q52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R52" s="3">
         <v>100</v>
@@ -4784,13 +4903,13 @@
         <v>100</v>
       </c>
       <c r="U52" s="3">
+        <v>100</v>
+      </c>
+      <c r="V52" s="3">
         <v>200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>100</v>
-      </c>
-      <c r="W52" s="3">
-        <v>200</v>
       </c>
       <c r="X52" s="3">
         <v>200</v>
@@ -4805,16 +4924,16 @@
         <v>200</v>
       </c>
       <c r="AB52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC52" s="3">
         <v>300</v>
       </c>
       <c r="AD52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="AE52" s="3">
+        <v>0</v>
       </c>
       <c r="AF52" s="3" t="s">
         <v>3</v>
@@ -4828,8 +4947,11 @@
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4929,95 +5051,98 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>499700</v>
+      </c>
+      <c r="E54" s="3">
         <v>481100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>477200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>482200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>436300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>433600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>421200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>408600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>401100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>368900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>363600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>369100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>292800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>281300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>259200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>171000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>151100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>135300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>118100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>125700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>118700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>119300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>98800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>105000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>96800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>95100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>39100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>41400</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5030,8 +5155,11 @@
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5067,8 +5195,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5104,95 +5233,96 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E57" s="3">
         <v>28500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>28800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>37200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>33900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>30100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>24600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>47300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>34200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>29800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>33200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>25400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>25900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>24300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>25200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>24500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>17400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>19900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>19000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>17700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>19800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>16800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>16900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>15300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12700</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5205,35 +5335,38 @@
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E58" s="3">
         <v>19000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>18500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>17000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>16100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>16900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5291,8 +5424,8 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>3</v>
+      <c r="AE58" s="3">
+        <v>0</v>
       </c>
       <c r="AF58" s="3" t="s">
         <v>3</v>
@@ -5306,95 +5439,98 @@
       <c r="AI58" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E59" s="3">
         <v>20100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>64100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>58600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>69600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>81400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>56100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>54700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>46000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>32000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>34300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>23600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>7800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4000</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5407,95 +5543,98 @@
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>141100</v>
+      </c>
+      <c r="E60" s="3">
         <v>115100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>105500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>106400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>105900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>97300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>89100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>82000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>111400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>92900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>99400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>114700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>81600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>80600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>63700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>56300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>59500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>48000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>32300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>32400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>31800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>27100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>27400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>24600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>25100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>21500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>18200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>16700</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5508,35 +5647,38 @@
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>161700</v>
+      </c>
+      <c r="E61" s="3">
         <v>163400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>165900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>157900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>144900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>149400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>142800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>133500</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5589,11 +5731,11 @@
         <v>0</v>
       </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>1500</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
@@ -5609,8 +5751,11 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5623,8 +5768,8 @@
       <c r="F62" s="3">
         <v>500</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
+      <c r="G62" s="3">
+        <v>500</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -5635,69 +5780,69 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>130200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>109900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>103500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>96600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>90700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>83700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>84700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1700</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>1600</v>
       </c>
       <c r="Z62" s="3">
         <v>1600</v>
       </c>
       <c r="AA62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AB62" s="3">
         <v>1400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1100</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5710,8 +5855,11 @@
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5811,8 +5959,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5912,8 +6063,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6013,95 +6167,98 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>303200</v>
+      </c>
+      <c r="E66" s="3">
         <v>278900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>271900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>264700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>250800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>246800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>232000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>215500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>241600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>202700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>202900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>211300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>172200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>164300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>148500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>63100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>65900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>53500</v>
-      </c>
-      <c r="U66" s="3">
-        <v>35500</v>
       </c>
       <c r="V66" s="3">
         <v>35500</v>
       </c>
       <c r="W66" s="3">
+        <v>35500</v>
+      </c>
+      <c r="X66" s="3">
         <v>34300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>28700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>29000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>26200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>26500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>22900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>20800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>17800</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6114,8 +6271,11 @@
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6151,8 +6311,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6252,8 +6413,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6353,8 +6517,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6454,8 +6621,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6555,95 +6725,98 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E72" s="3">
         <v>15600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>21400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>34400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-15700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-8300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-14200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-15900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-50200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-52900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-61400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-63400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-85100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-87600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-86500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-78200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-83600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-76800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-72100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-63000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-71400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-68900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-61900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-56300</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6656,8 +6829,11 @@
       <c r="AI72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6757,8 +6933,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6858,8 +7037,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6959,95 +7141,98 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>196500</v>
+      </c>
+      <c r="E76" s="3">
         <v>202100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>205300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>217500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>185500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>186800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>189300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>193100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>159400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>166200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>160700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>157800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>120600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>116900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>110700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>107900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>85300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>81800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>82600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>90200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>84400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>90600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>69700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>78800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>70300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>72200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>18300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>23600</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7060,8 +7245,11 @@
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7161,215 +7349,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45599</v>
+      </c>
+      <c r="E80" s="2">
         <v>45508</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45417</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45326</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45228</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45137</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44955</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44864</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44682</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44591</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44409</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44318</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44227</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44136</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44045</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43954</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43863</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43772</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43681</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43590</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43499</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43408</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43317</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43226</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43135</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43037</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42946</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42855</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42582</v>
       </c>
-      <c r="AI80" s="2" t="s">
+      <c r="AJ80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>31000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>26200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>34200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>8400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>21700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>8400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-33700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-6400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-6300</v>
       </c>
-      <c r="AI81" s="3" t="s">
+      <c r="AJ81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7405,109 +7602,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E83" s="3">
         <v>2900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>800</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>700</v>
       </c>
       <c r="AD83" s="3">
         <v>700</v>
       </c>
       <c r="AE83" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF83" s="3">
         <v>800</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>300</v>
       </c>
       <c r="AG83" s="3">
         <v>300</v>
       </c>
       <c r="AH83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI83" s="3">
         <v>1200</v>
       </c>
-      <c r="AI83" s="3" t="s">
+      <c r="AJ83" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7607,8 +7808,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7708,8 +7912,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7809,8 +8016,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7910,8 +8120,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8011,109 +8224,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E89" s="3">
         <v>6200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>56300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>21100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>47000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-37600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-21800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>49200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-15900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>33600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>12600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>25200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-13400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-14900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>7200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>6800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-6300</v>
       </c>
-      <c r="AI89" s="3" t="s">
+      <c r="AJ89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8149,109 +8368,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI91" s="3" t="s">
+      <c r="AJ91" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8351,8 +8574,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8452,109 +8678,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3100</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-1900</v>
       </c>
       <c r="S94" s="3">
         <v>-1900</v>
       </c>
       <c r="T94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="U94" s="3">
         <v>-2900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>-2300</v>
       </c>
       <c r="AF94" s="3">
         <v>-2300</v>
       </c>
       <c r="AG94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI94" s="3" t="s">
+      <c r="AJ94" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8590,8 +8822,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8616,8 +8849,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8691,8 +8924,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8792,8 +9028,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8893,8 +9132,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8994,109 +9236,115 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-3100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-500</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-100</v>
       </c>
       <c r="K100" s="3">
         <v>-100</v>
       </c>
       <c r="L100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M100" s="3">
         <v>-1500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-900</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>25400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-300</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>57400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>7900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>6400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>5300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>8400</v>
       </c>
-      <c r="AI100" s="3" t="s">
+      <c r="AJ100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9121,8 +9369,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9196,105 +9444,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>49300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-17000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>39700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-46700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-28000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>44500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-20600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-12600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>30700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>20600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-16300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>8500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>4400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>46300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-7200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>4900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>700</v>
       </c>
-      <c r="AI102" s="3" t="s">
+      <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
   <si>
     <t>LOVE</t>
   </si>
@@ -656,470 +656,483 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E7" s="2">
         <v>45599</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45508</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45417</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45326</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45228</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45137</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44955</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44864</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44682</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44591</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44409</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44318</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44136</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44045</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43954</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43863</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43772</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43681</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43590</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43499</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43408</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43317</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43226</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43135</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43037</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42946</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42855</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42582</v>
       </c>
-      <c r="AJ7" s="2" t="s">
+      <c r="AK7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>241500</v>
+      </c>
+      <c r="E8" s="3">
         <v>149900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>156600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>132600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>250500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>154000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>154500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>141200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>238500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>134800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>148500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>129400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>196200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>116700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>102400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>82900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>129700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>74700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>61900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>54400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>92200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>52100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>48100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>41000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>64200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>41700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>33200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>26800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>39000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>24400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>20700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>17600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>30500</v>
       </c>
-      <c r="AJ8" s="3" t="s">
+      <c r="AK8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>95700</v>
+      </c>
+      <c r="E9" s="3">
         <v>62300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>64200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>60600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>100900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>65600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>62100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>70600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>104800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>69900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>69400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>63400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>173600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>58100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>43400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>36800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>54600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>33400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>30900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>27100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>47000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>25800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>23900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>20000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>28700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>18800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>15400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>16100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>10700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>9200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>14700</v>
       </c>
-      <c r="AJ9" s="3" t="s">
+      <c r="AK9" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>145800</v>
+      </c>
+      <c r="E10" s="3">
         <v>87600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>92400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>72000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>149600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>88400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>92400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>70600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>133700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>64900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>79100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>66000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>22600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>58600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>59000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>46100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>75100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>41300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>31000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>27300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>45200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>26300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>24200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>21000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>35500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>22900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>17800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>14700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>22900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>13700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>11500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>9100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>15800</v>
       </c>
-      <c r="AJ10" s="3" t="s">
+      <c r="AK10" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1156,8 +1169,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1260,8 +1274,11 @@
       <c r="AJ12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1364,8 +1381,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1402,24 +1422,24 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>-600</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>600</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
         <v>200</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1435,8 +1455,8 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1468,101 +1488,104 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E15" s="3">
         <v>3700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>3500</v>
       </c>
       <c r="G15" s="3">
         <v>3500</v>
       </c>
       <c r="H15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I15" s="3">
         <v>3300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>700</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF15" s="3">
+      <c r="AF15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG15" s="3">
         <v>800</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1572,8 +1595,11 @@
       <c r="AJ15" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK15" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1607,216 +1633,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>193900</v>
+      </c>
+      <c r="E17" s="3">
         <v>157600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>165000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>150500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>210100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>157600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>155500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>146900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>202000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>144900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>140400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>126900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>169900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>113700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>93400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>80700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>107900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>72200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>63000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>62800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>86800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>59000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>53100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>50300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>55900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>44400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>40200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>32400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>36500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>26500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>23100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>20800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>36500</v>
       </c>
-      <c r="AJ17" s="3" t="s">
+      <c r="AK17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-17900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>40400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>36500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>26300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>21800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>8300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-5600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-6000</v>
       </c>
-      <c r="AJ18" s="3" t="s">
+      <c r="AK18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1853,8 +1886,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1882,33 +1916,33 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1916,13 +1950,13 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3">
         <v>100</v>
       </c>
       <c r="Y20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z20" s="3">
         <v>200</v>
@@ -1934,10 +1968,10 @@
         <v>200</v>
       </c>
       <c r="AC20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AD20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE20" s="3">
         <v>-100</v>
@@ -1946,123 +1980,129 @@
         <v>-100</v>
       </c>
       <c r="AG20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-100</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="3" t="s">
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-14400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>43800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>39100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>11200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>28400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>10600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>23300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-6700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>6900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AJ21" s="3" t="s">
+      <c r="AK21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2087,8 +2127,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2160,168 +2200,174 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>300</v>
       </c>
-      <c r="AJ22" s="3" t="s">
+      <c r="AK22" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>48300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>41200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>36500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>26300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>9000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>21700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-6300</v>
       </c>
-      <c r="AJ23" s="3" t="s">
+      <c r="AK23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-4200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>10200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1000</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>10200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-7900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
@@ -2361,8 +2407,8 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>3</v>
+      <c r="AG24" s="3">
+        <v>0</v>
       </c>
       <c r="AH24" s="3" t="s">
         <v>3</v>
@@ -2373,8 +2419,11 @@
       <c r="AJ24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2477,216 +2526,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>31000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>26200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>34200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>8400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>21700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>8400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-6300</v>
       </c>
-      <c r="AJ26" s="3" t="s">
+      <c r="AK26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>31000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>26200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>34200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>8400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>21700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>8400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-33700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-6400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-6300</v>
       </c>
-      <c r="AJ27" s="3" t="s">
+      <c r="AK27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2789,8 +2847,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2893,8 +2954,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2997,8 +3061,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3101,8 +3168,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3130,33 +3200,33 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -3164,13 +3234,13 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X32" s="3">
         <v>-100</v>
       </c>
       <c r="Y32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Z32" s="3">
         <v>-200</v>
@@ -3182,10 +3252,10 @@
         <v>-200</v>
       </c>
       <c r="AC32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AD32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE32" s="3">
         <v>100</v>
@@ -3194,123 +3264,129 @@
         <v>100</v>
       </c>
       <c r="AG32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>100</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="3" t="s">
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>31000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>26200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>34200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>8400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>21700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>8400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-33700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-6300</v>
       </c>
-      <c r="AJ33" s="3" t="s">
+      <c r="AK33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3413,221 +3489,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>31000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>26200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>34200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>8400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>21700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>8400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-33700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-6300</v>
       </c>
-      <c r="AJ35" s="3" t="s">
+      <c r="AK35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E38" s="2">
         <v>45599</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45508</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45417</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45326</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45228</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45137</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44955</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44864</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44682</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44591</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44409</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44318</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44136</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44045</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43954</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43863</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43772</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43681</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43590</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43499</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43408</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43317</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43226</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43135</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43037</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42946</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42855</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42582</v>
       </c>
-      <c r="AJ38" s="2" t="s">
+      <c r="AK38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3664,8 +3749,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3702,98 +3788,99 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>83700</v>
+      </c>
+      <c r="E41" s="3">
         <v>61700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>72100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>72400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>87000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>37700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>54700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>45100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>43500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>64400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>92400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>47900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>68500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>65700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>78300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>47700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>54800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>45500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>48500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>27900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>44200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>35700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>49100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>44700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>48200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>9200</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3806,8 +3893,11 @@
       <c r="AJ41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3910,98 +4000,101 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E43" s="3">
         <v>16100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>13000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>18400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2800</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4014,98 +4107,101 @@
       <c r="AJ43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>124300</v>
+      </c>
+      <c r="E44" s="3">
         <v>113400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>88300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>94700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>98400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>116600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>105000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>104500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>119600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>154500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>145700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>123000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>108500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>94500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>75000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>56000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>50400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>57800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>41000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>33400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>36400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>50200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>40700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>30900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>26200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>24600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>20200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>13900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>11600</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4118,98 +4214,101 @@
       <c r="AJ44" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK44" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E45" s="3">
         <v>2000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3800</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>5100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>35600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>31200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>11600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>6300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>6300</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>5800</v>
       </c>
       <c r="AD45" s="3">
         <v>5800</v>
       </c>
       <c r="AE45" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AF45" s="3">
         <v>6100</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4222,98 +4321,101 @@
       <c r="AJ45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>246600</v>
+      </c>
+      <c r="E46" s="3">
         <v>209900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>194200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>190800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>214400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>184300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>183600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>181500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>187700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>209300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>203500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>206200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>221700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>163600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>161400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>140200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>143400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>123500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>107800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>91900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>100200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>95400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>97500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>78000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>85100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>78500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>78300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>24900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>29700</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4326,8 +4428,11 @@
       <c r="AJ46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4355,8 +4460,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4430,98 +4535,101 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>235700</v>
+      </c>
+      <c r="E48" s="3">
         <v>234900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>236100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>239500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>226700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>212300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>212400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>202800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>188300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>179500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>155300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>145400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>135000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>127700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>118400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>117600</v>
-      </c>
-      <c r="S48" s="3">
-        <v>25900</v>
       </c>
       <c r="T48" s="3">
         <v>25900</v>
       </c>
       <c r="U48" s="3">
+        <v>25900</v>
+      </c>
+      <c r="V48" s="3">
         <v>25700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>24400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>23800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>21800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>18600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>17100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>15700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>11000</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4534,8 +4642,11 @@
       <c r="AJ48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4543,7 +4654,7 @@
         <v>1700</v>
       </c>
       <c r="E49" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="F49" s="3">
         <v>1600</v>
@@ -4564,10 +4675,10 @@
         <v>1600</v>
       </c>
       <c r="L49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M49" s="3">
         <v>2900</v>
-      </c>
-      <c r="M49" s="3">
-        <v>3000</v>
       </c>
       <c r="N49" s="3">
         <v>3000</v>
@@ -4576,55 +4687,55 @@
         <v>3000</v>
       </c>
       <c r="P49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Q49" s="3">
         <v>1500</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>1300</v>
       </c>
       <c r="R49" s="3">
         <v>1300</v>
       </c>
       <c r="S49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T49" s="3">
         <v>1700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1200</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>1100</v>
       </c>
       <c r="AA49" s="3">
         <v>1100</v>
       </c>
       <c r="AB49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC49" s="3">
         <v>1000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>800</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>700</v>
       </c>
       <c r="AE49" s="3">
         <v>700</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>3</v>
+      <c r="AF49" s="3">
+        <v>700</v>
       </c>
       <c r="AG49" s="3" t="s">
         <v>3</v>
@@ -4638,8 +4749,11 @@
       <c r="AJ49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4742,8 +4856,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4846,55 +4963,58 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E52" s="3">
         <v>34100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>32300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>30400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>28700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>26900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>25900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10800</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
       <c r="R52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S52" s="3">
         <v>100</v>
@@ -4906,13 +5026,13 @@
         <v>100</v>
       </c>
       <c r="V52" s="3">
+        <v>100</v>
+      </c>
+      <c r="W52" s="3">
         <v>200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>100</v>
-      </c>
-      <c r="X52" s="3">
-        <v>200</v>
       </c>
       <c r="Y52" s="3">
         <v>200</v>
@@ -4927,16 +5047,16 @@
         <v>200</v>
       </c>
       <c r="AC52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AD52" s="3">
         <v>300</v>
       </c>
       <c r="AE52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF52" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>0</v>
       </c>
       <c r="AG52" s="3" t="s">
         <v>3</v>
@@ -4950,8 +5070,11 @@
       <c r="AJ52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5054,98 +5177,101 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>532300</v>
+      </c>
+      <c r="E54" s="3">
         <v>499700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>481100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>477200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>482200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>436300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>433600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>421200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>408600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>401100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>368900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>363600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>369100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>292800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>281300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>259200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>171000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>151100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>135300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>118100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>125700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>118700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>119300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>98800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>105000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>96800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>95100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>39100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>41400</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5158,8 +5284,11 @@
       <c r="AJ54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5196,8 +5325,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5234,98 +5364,99 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E57" s="3">
         <v>48700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>28100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>28800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>37200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>33900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>30100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>47300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>34200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>29800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>33200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>25400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>25900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>24300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>25200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>24500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>17400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>19900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>19000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>17700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>19800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>16800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>16900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>15300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12700</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5338,38 +5469,41 @@
       <c r="AJ57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E58" s="3">
         <v>21200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>19000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>17600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>17000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>16100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>16900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13100</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5427,8 +5561,8 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>3</v>
+      <c r="AF58" s="3">
+        <v>0</v>
       </c>
       <c r="AG58" s="3" t="s">
         <v>3</v>
@@ -5442,98 +5576,101 @@
       <c r="AJ58" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E59" s="3">
         <v>21200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>64100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>58600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>69600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>81400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>56100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>54700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>46000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>32000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>34300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>23600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>7700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>7800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>6200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4000</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5546,98 +5683,101 @@
       <c r="AJ59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>155100</v>
+      </c>
+      <c r="E60" s="3">
         <v>141100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>115100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>105500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>106400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>105900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>97300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>89100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>82000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>111400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>92900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>99400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>114700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>81600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>80600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>63700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>56300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>59500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>48000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>32300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>32400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>31800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>27100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>27400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>24600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>25100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>21500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>18200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>16700</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5650,38 +5790,41 @@
       <c r="AJ60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>160400</v>
+      </c>
+      <c r="E61" s="3">
         <v>161700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>163400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>165900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>157900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>144900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>149400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>142800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>133500</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5734,11 +5877,11 @@
         <v>0</v>
       </c>
       <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>1500</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
@@ -5754,13 +5897,16 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
         <v>500</v>
@@ -5771,8 +5917,8 @@
       <c r="G62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+      <c r="H62" s="3">
+        <v>500</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -5783,69 +5929,69 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>130200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>109900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>103500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>96600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>90700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>83700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>84700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1700</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>1600</v>
       </c>
       <c r="AA62" s="3">
         <v>1600</v>
       </c>
       <c r="AB62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AC62" s="3">
         <v>1400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1100</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5858,8 +6004,11 @@
       <c r="AJ62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5962,8 +6111,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6066,8 +6218,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6170,98 +6325,101 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>315900</v>
+      </c>
+      <c r="E66" s="3">
         <v>303200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>278900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>271900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>264700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>250800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>246800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>232000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>215500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>241600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>202700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>202900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>211300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>172200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>164300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>148500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>63100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>65900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>53500</v>
-      </c>
-      <c r="V66" s="3">
-        <v>35500</v>
       </c>
       <c r="W66" s="3">
         <v>35500</v>
       </c>
       <c r="X66" s="3">
+        <v>35500</v>
+      </c>
+      <c r="Y66" s="3">
         <v>34300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>28700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>29000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>26200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>22900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>20800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>17800</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6274,8 +6432,11 @@
       <c r="AJ66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6312,8 +6473,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6416,8 +6578,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6520,8 +6685,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6624,8 +6792,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6728,98 +6899,101 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E72" s="3">
         <v>7200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>21400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>34400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-15700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-8300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-14200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-15900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-50200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-52900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-61400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-63400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-85100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-87600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-86500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-78200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-83600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-76800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-72100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-63000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-71400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-68900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-61900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-56300</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6832,8 +7006,11 @@
       <c r="AJ72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6936,8 +7113,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7040,8 +7220,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7144,98 +7327,101 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>216400</v>
+      </c>
+      <c r="E76" s="3">
         <v>196500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>202100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>205300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>217500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>185500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>186800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>189300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>193100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>159400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>166200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>160700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>157800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>120600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>116900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>110700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>107900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>85300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>81800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>82600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>90200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>84400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>90600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>69700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>78800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>70300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>72200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>18300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>23600</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7248,8 +7434,11 @@
       <c r="AJ76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7352,221 +7541,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E80" s="2">
         <v>45599</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45508</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45417</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45326</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45228</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45137</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44955</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44864</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44682</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44591</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44409</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44318</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44136</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44045</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43954</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43863</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43772</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43681</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43590</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43499</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43408</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43317</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43226</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43135</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43037</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42946</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42855</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42582</v>
       </c>
-      <c r="AJ80" s="2" t="s">
+      <c r="AK80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>31000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>26200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>34200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>8400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>21700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>8400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-33700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-6300</v>
       </c>
-      <c r="AJ81" s="3" t="s">
+      <c r="AK81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7603,112 +7801,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E83" s="3">
         <v>3200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>800</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>700</v>
       </c>
       <c r="AE83" s="3">
         <v>700</v>
       </c>
       <c r="AF83" s="3">
+        <v>700</v>
+      </c>
+      <c r="AG83" s="3">
         <v>800</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>300</v>
       </c>
       <c r="AH83" s="3">
         <v>300</v>
       </c>
       <c r="AI83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ83" s="3" t="s">
+      <c r="AK83" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7811,8 +8013,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7915,8 +8120,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8019,8 +8227,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8123,8 +8334,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8227,112 +8441,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>56300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>21100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>47000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-37600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-21800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>49200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-15900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-9600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>33600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>12600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>25200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-14900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>7200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>6800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-6300</v>
       </c>
-      <c r="AJ89" s="3" t="s">
+      <c r="AK89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8369,112 +8589,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ91" s="3" t="s">
+      <c r="AK91" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8577,8 +8801,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8681,112 +8908,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3100</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-1900</v>
       </c>
       <c r="T94" s="3">
         <v>-1900</v>
       </c>
       <c r="U94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="V94" s="3">
         <v>-2900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>-2300</v>
       </c>
       <c r="AG94" s="3">
         <v>-2300</v>
       </c>
       <c r="AH94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ94" s="3" t="s">
+      <c r="AK94" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8823,8 +9056,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8852,8 +9086,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8927,8 +9161,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9031,8 +9268,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9135,8 +9375,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9239,112 +9482,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-400</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-3100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-500</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-100</v>
       </c>
       <c r="L100" s="3">
         <v>-100</v>
       </c>
       <c r="M100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N100" s="3">
         <v>-1500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-900</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>25400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-300</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>57400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>7900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>6400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>5300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>8400</v>
       </c>
-      <c r="AJ100" s="3" t="s">
+      <c r="AK100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9372,8 +9621,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9447,108 +9696,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-10400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-14700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>49300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>39700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-46700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-28000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>44500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>30700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-7100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>9400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>20600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-16300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>8500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>46300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-7200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>3500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>700</v>
       </c>
-      <c r="AJ102" s="3" t="s">
+      <c r="AK102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
   <si>
     <t>LOVE</t>
   </si>
@@ -656,483 +656,496 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45781</v>
+      </c>
+      <c r="E7" s="2">
         <v>45690</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45599</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45508</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45417</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45326</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45228</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45137</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44955</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44864</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44682</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44591</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44409</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44318</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44136</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44045</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43954</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43863</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43772</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43681</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43590</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43499</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43408</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43317</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43226</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43135</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43037</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42946</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42582</v>
       </c>
-      <c r="AK7" s="2" t="s">
+      <c r="AL7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>138400</v>
+      </c>
+      <c r="E8" s="3">
         <v>241500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>149900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>156600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>132600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>250500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>154000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>154500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>141200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>238500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>134800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>148500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>129400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>196200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>116700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>102400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>82900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>129700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>74700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>61900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>54400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>92200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>52100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>48100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>41000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>64200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>41700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>33200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>26800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>39000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>24400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>20700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>17600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>30500</v>
       </c>
-      <c r="AK8" s="3" t="s">
+      <c r="AL8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E9" s="3">
         <v>95700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>62300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>64200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>60600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>100900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>65600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>62100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>70600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>104800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>69900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>69400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>63400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>173600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>58100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>43400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>36800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>54600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>33400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>30900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>27100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>47000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>25800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>23900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>20000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>28700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>18800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>15400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>16100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>10700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>9200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>14700</v>
       </c>
-      <c r="AK9" s="3" t="s">
+      <c r="AL9" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>74400</v>
+      </c>
+      <c r="E10" s="3">
         <v>145800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>87600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>92400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>72000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>149600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>88400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>92400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>70600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>133700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>64900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>79100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>66000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>22600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>58600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>59000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>46100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>75100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>41300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>31000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>27300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>45200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>26300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>24200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>21000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>35500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>22900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>17800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>14700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>22900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>13700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>11500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>15800</v>
       </c>
-      <c r="AK10" s="3" t="s">
+      <c r="AL10" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1170,8 +1183,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1277,8 +1291,11 @@
       <c r="AK12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1384,8 +1401,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1425,24 +1445,24 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-600</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>600</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
         <v>200</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1458,8 +1478,8 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1491,104 +1511,107 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E15" s="3">
         <v>3800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3800</v>
-      </c>
-      <c r="G15" s="3">
-        <v>3500</v>
       </c>
       <c r="H15" s="3">
         <v>3500</v>
       </c>
       <c r="I15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J15" s="3">
         <v>3300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>700</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG15" s="3">
+      <c r="AG15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH15" s="3">
         <v>800</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1598,8 +1621,11 @@
       <c r="AK15" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL15" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1634,222 +1660,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>153300</v>
+      </c>
+      <c r="E17" s="3">
         <v>193900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>157600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>165000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>150500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>210100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>157600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>155500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>146900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>202000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>144900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>140400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>126900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>169900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>113700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>93400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>80700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>107900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>72200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>63000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>62800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>86800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>59000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>53100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>50300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>55900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>44400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>40200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>32400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>36500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>26500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>23100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>20800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>36500</v>
       </c>
-      <c r="AK17" s="3" t="s">
+      <c r="AL17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E18" s="3">
         <v>47600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-17900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>40400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>36500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>26300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>21800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>8300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-5600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-6000</v>
       </c>
-      <c r="AK18" s="3" t="s">
+      <c r="AL18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1887,13 +1920,14 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
@@ -1919,33 +1953,33 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1953,13 +1987,13 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3">
         <v>100</v>
       </c>
       <c r="Z20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA20" s="3">
         <v>200</v>
@@ -1971,10 +2005,10 @@
         <v>200</v>
       </c>
       <c r="AD20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AE20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF20" s="3">
         <v>-100</v>
@@ -1983,126 +2017,132 @@
         <v>-100</v>
       </c>
       <c r="AH20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="3" t="s">
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E21" s="3">
         <v>51400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-14400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>43800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>39100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>28400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>10600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>23300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-6700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-6200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AK21" s="3" t="s">
+      <c r="AL21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2130,8 +2170,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2203,174 +2243,180 @@
         <v>0</v>
       </c>
       <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3">
         <v>300</v>
       </c>
-      <c r="AK22" s="3" t="s">
+      <c r="AL22" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E23" s="3">
         <v>48300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>41200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>36500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>26300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>9000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>21700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-9100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-6300</v>
       </c>
-      <c r="AK23" s="3" t="s">
+      <c r="AL23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E24" s="3">
         <v>13000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-4200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>10200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1000</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>10200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
@@ -2410,8 +2456,8 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>3</v>
+      <c r="AH24" s="3">
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="s">
         <v>3</v>
@@ -2422,8 +2468,11 @@
       <c r="AK24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2529,222 +2578,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E26" s="3">
         <v>35300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>31000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>26200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>34200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>8400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>21700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-9100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>8400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-6300</v>
       </c>
-      <c r="AK26" s="3" t="s">
+      <c r="AL26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E27" s="3">
         <v>35300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-13000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>31000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>26200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>34200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>8400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>21700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-9100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>8400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-33700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-6400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-6300</v>
       </c>
-      <c r="AK27" s="3" t="s">
+      <c r="AL27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2850,8 +2908,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2957,8 +3018,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3064,8 +3128,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3171,13 +3238,16 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
@@ -3203,33 +3273,33 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -3237,13 +3307,13 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="3">
         <v>-100</v>
       </c>
       <c r="Z32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AA32" s="3">
         <v>-200</v>
@@ -3255,10 +3325,10 @@
         <v>-200</v>
       </c>
       <c r="AD32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AE32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF32" s="3">
         <v>100</v>
@@ -3267,126 +3337,132 @@
         <v>100</v>
       </c>
       <c r="AH32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>100</v>
       </c>
-      <c r="AJ32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK32" s="3" t="s">
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E33" s="3">
         <v>35300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>31000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>26200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>34200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>8400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>21700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-9100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>8400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-33700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-6400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-6300</v>
       </c>
-      <c r="AK33" s="3" t="s">
+      <c r="AL33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3492,227 +3568,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E35" s="3">
         <v>35300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>31000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>26200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>34200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>8400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>21700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-9100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>8400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-33700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-6400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-6300</v>
       </c>
-      <c r="AK35" s="3" t="s">
+      <c r="AL35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45781</v>
+      </c>
+      <c r="E38" s="2">
         <v>45690</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45599</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45508</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45417</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45326</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45228</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45137</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44955</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44864</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44682</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44591</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44409</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44318</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44136</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44045</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43954</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43863</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43772</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43681</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43590</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43499</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43408</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43317</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43226</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43135</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43037</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42946</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42582</v>
       </c>
-      <c r="AK38" s="2" t="s">
+      <c r="AL38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3750,8 +3835,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3789,101 +3875,102 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E41" s="3">
         <v>83700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>61700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>72100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>72400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>87000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>37700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>54700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>45100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>43500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>64400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>92400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>47900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>68500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>65700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>78300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>47700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>54800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>45500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>48500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>27900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>44200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>35700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>49100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>44700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>48200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>9200</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3896,8 +3983,11 @@
       <c r="AK41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4003,101 +4093,104 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E43" s="3">
         <v>16800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>16100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>13500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>18400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2800</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4110,101 +4203,104 @@
       <c r="AK43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>124900</v>
+      </c>
+      <c r="E44" s="3">
         <v>124300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>113400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>88300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>94700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>98400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>116600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>105000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>104500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>119600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>154500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>145700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>123000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>108500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>94500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>75000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>56000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>50400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>57800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>41000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>33400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>36400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>50200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>40700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>30900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>26200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>24600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>20200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>13900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>11600</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,101 +4313,104 @@
       <c r="AK44" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL44" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E45" s="3">
         <v>6900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3800</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>5100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>35600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>11400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>11600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>5900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>6300</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>5800</v>
       </c>
       <c r="AE45" s="3">
         <v>5800</v>
       </c>
       <c r="AF45" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AG45" s="3">
         <v>6100</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4324,101 +4423,104 @@
       <c r="AK45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>181500</v>
+      </c>
+      <c r="E46" s="3">
         <v>246600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>209900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>194200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>190800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>214400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>184300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>183600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>181500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>187700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>209300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>203500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>206200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>221700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>163600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>161400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>140200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>143400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>123500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>107800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>91900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>100200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>95400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>97500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>78000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>85100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>78500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>78300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>24900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>29700</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4431,8 +4533,11 @@
       <c r="AK46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4463,8 +4568,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4538,101 +4643,104 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>249500</v>
+      </c>
+      <c r="E48" s="3">
         <v>235700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>234900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>236100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>239500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>226700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>212300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>212400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>202800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>188300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>179500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>155300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>145400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>135000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>127700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>118400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>117600</v>
-      </c>
-      <c r="T48" s="3">
-        <v>25900</v>
       </c>
       <c r="U48" s="3">
         <v>25900</v>
       </c>
       <c r="V48" s="3">
+        <v>25900</v>
+      </c>
+      <c r="W48" s="3">
         <v>25700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>24400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>23800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>21800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>18600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>17100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>15700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>11000</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4645,19 +4753,22 @@
       <c r="AK48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="E49" s="3">
         <v>1700</v>
       </c>
       <c r="F49" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="G49" s="3">
         <v>1600</v>
@@ -4678,10 +4789,10 @@
         <v>1600</v>
       </c>
       <c r="M49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N49" s="3">
         <v>2900</v>
-      </c>
-      <c r="N49" s="3">
-        <v>3000</v>
       </c>
       <c r="O49" s="3">
         <v>3000</v>
@@ -4690,55 +4801,55 @@
         <v>3000</v>
       </c>
       <c r="Q49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R49" s="3">
         <v>1500</v>
-      </c>
-      <c r="R49" s="3">
-        <v>1300</v>
       </c>
       <c r="S49" s="3">
         <v>1300</v>
       </c>
       <c r="T49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U49" s="3">
         <v>1700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1200</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>1100</v>
       </c>
       <c r="AB49" s="3">
         <v>1100</v>
       </c>
       <c r="AC49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD49" s="3">
         <v>1000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>800</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>700</v>
       </c>
       <c r="AF49" s="3">
         <v>700</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>3</v>
+      <c r="AG49" s="3">
+        <v>700</v>
       </c>
       <c r="AH49" s="3" t="s">
         <v>3</v>
@@ -4752,8 +4863,11 @@
       <c r="AK49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4859,8 +4973,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4966,58 +5083,61 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E52" s="3">
         <v>32900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>34100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>32300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>30400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>28700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>26900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>22400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10800</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
       <c r="S52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T52" s="3">
         <v>100</v>
@@ -5029,13 +5149,13 @@
         <v>100</v>
       </c>
       <c r="W52" s="3">
+        <v>100</v>
+      </c>
+      <c r="X52" s="3">
         <v>200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>100</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>200</v>
       </c>
       <c r="Z52" s="3">
         <v>200</v>
@@ -5050,16 +5170,16 @@
         <v>200</v>
       </c>
       <c r="AD52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AE52" s="3">
         <v>300</v>
       </c>
       <c r="AF52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG52" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
       </c>
       <c r="AH52" s="3" t="s">
         <v>3</v>
@@ -5073,8 +5193,11 @@
       <c r="AK52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5180,101 +5303,104 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>483700</v>
+      </c>
+      <c r="E54" s="3">
         <v>532300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>499700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>481100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>477200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>482200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>436300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>433600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>421200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>408600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>401100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>368900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>363600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>369100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>292800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>281300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>259200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>171000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>151100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>135300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>118100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>125700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>118700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>119300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>98800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>105000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>96800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>95100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>39100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>41400</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5287,8 +5413,11 @@
       <c r="AK54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5326,8 +5455,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5365,101 +5495,102 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E57" s="3">
         <v>51800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>48700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>28500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>28100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>28800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>37200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>33900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>30100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>24600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>47300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>34200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>29800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>33200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>25400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>25900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>17700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>24300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>25200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>24500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>17400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>19900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>19000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>17700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>19800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>16800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>16900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>15300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12700</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5472,41 +5603,44 @@
       <c r="AK57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E58" s="3">
         <v>22700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>21200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>17600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>17000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>16100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>16900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13100</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5564,8 +5698,8 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>3</v>
+      <c r="AG58" s="3">
+        <v>0</v>
       </c>
       <c r="AH58" s="3" t="s">
         <v>3</v>
@@ -5579,101 +5713,104 @@
       <c r="AK58" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E59" s="3">
         <v>31900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>64100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>58600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>69600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>81400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>56100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>54700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>46000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>32000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>34300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>23600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>14900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>12800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>7700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>6200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4000</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5686,101 +5823,104 @@
       <c r="AK59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>113100</v>
+      </c>
+      <c r="E60" s="3">
         <v>155100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>141100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>115100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>105500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>106400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>105900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>97300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>89100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>82000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>111400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>92900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>99400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>114700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>81600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>80600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>63700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>56300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>59500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>48000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>32300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>32400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>31800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>27100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>27400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>24600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>25100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>21500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>18200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>16700</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5793,41 +5933,44 @@
       <c r="AK60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>169000</v>
+      </c>
+      <c r="E61" s="3">
         <v>160400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>161700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>163400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>165900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>157900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>144900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>149400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>142800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>133500</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5880,11 +6023,11 @@
         <v>0</v>
       </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>1500</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
@@ -5900,8 +6043,11 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5909,7 +6055,7 @@
         <v>400</v>
       </c>
       <c r="E62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F62" s="3">
         <v>500</v>
@@ -5920,8 +6066,8 @@
       <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+      <c r="I62" s="3">
+        <v>500</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -5932,69 +6078,69 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>130200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>109900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>103500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>96600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>90700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>83700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>84700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1700</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>1600</v>
       </c>
       <c r="AB62" s="3">
         <v>1600</v>
       </c>
       <c r="AC62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AD62" s="3">
         <v>1400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1100</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>3</v>
       </c>
@@ -6007,8 +6153,11 @@
       <c r="AK62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6114,8 +6263,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6221,8 +6373,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6328,101 +6483,104 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>282500</v>
+      </c>
+      <c r="E66" s="3">
         <v>315900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>303200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>278900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>271900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>264700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>250800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>246800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>232000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>215500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>241600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>202700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>202900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>211300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>172200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>164300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>148500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>63100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>65900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>53500</v>
-      </c>
-      <c r="W66" s="3">
-        <v>35500</v>
       </c>
       <c r="X66" s="3">
         <v>35500</v>
       </c>
       <c r="Y66" s="3">
+        <v>35500</v>
+      </c>
+      <c r="Z66" s="3">
         <v>34300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>28700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>29000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>26500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>22900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>20800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>17800</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6435,8 +6593,11 @@
       <c r="AK66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6474,8 +6635,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6581,8 +6743,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6688,8 +6853,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6795,8 +6963,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6902,101 +7073,104 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E72" s="3">
         <v>25800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>21400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>34400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-15700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-8300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-14200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-15900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-50200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-52900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-61400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-63400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-85100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-87600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-86500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-78200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-83600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-76800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-72100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-63000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-71400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-68900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-61900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-56300</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7009,8 +7183,11 @@
       <c r="AK72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7116,8 +7293,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7223,8 +7403,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7330,101 +7513,104 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>201200</v>
+      </c>
+      <c r="E76" s="3">
         <v>216400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>196500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>202100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>205300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>217500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>185500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>186800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>189300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>193100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>159400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>166200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>160700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>157800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>120600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>116900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>110700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>107900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>85300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>81800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>82600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>90200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>84400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>90600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>69700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>78800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>70300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>72200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>18300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>23600</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7437,8 +7623,11 @@
       <c r="AK76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7544,227 +7733,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45781</v>
+      </c>
+      <c r="E80" s="2">
         <v>45690</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45599</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45508</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45417</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45326</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45228</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45137</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44955</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44864</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44682</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44591</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44409</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44318</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44136</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44045</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43954</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43863</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43772</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43681</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43590</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43499</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43408</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43317</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43226</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43135</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43037</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42946</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42582</v>
       </c>
-      <c r="AK80" s="2" t="s">
+      <c r="AL80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E81" s="3">
         <v>35300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>31000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>26200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>34200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>8400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>21700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-9100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>8400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-33700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-6400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-6300</v>
       </c>
-      <c r="AK81" s="3" t="s">
+      <c r="AL81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7802,8 +8000,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7811,106 +8010,109 @@
         <v>3400</v>
       </c>
       <c r="E83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F83" s="3">
         <v>3200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>800</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>700</v>
       </c>
       <c r="AF83" s="3">
         <v>700</v>
       </c>
       <c r="AG83" s="3">
+        <v>700</v>
+      </c>
+      <c r="AH83" s="3">
         <v>800</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>300</v>
       </c>
       <c r="AI83" s="3">
         <v>300</v>
       </c>
       <c r="AJ83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AK83" s="3">
         <v>1200</v>
       </c>
-      <c r="AK83" s="3" t="s">
+      <c r="AL83" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8016,8 +8218,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8123,8 +8328,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8230,8 +8438,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8337,8 +8548,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8444,115 +8658,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-41400</v>
+      </c>
+      <c r="E89" s="3">
         <v>44000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>56300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>21100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>47000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-37600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-21800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>49200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-15900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>10400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-9600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>33600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-5100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>12600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>25200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-14900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-8200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>6800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-4600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-6300</v>
       </c>
-      <c r="AK89" s="3" t="s">
+      <c r="AL89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8590,115 +8810,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AK91" s="3" t="s">
+      <c r="AL91" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8804,8 +9028,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8911,115 +9138,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3100</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-1900</v>
       </c>
       <c r="U94" s="3">
         <v>-1900</v>
       </c>
       <c r="V94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="W94" s="3">
         <v>-2900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AG94" s="3">
-        <v>-2300</v>
       </c>
       <c r="AH94" s="3">
         <v>-2300</v>
       </c>
       <c r="AI94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AK94" s="3" t="s">
+      <c r="AL94" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9057,8 +9290,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9089,8 +9323,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9164,8 +9398,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9271,8 +9508,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9378,8 +9618,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9485,115 +9728,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-16500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-400</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-3100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-500</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-100</v>
       </c>
       <c r="M100" s="3">
         <v>-100</v>
       </c>
       <c r="N100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O100" s="3">
         <v>-1500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-900</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>25400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-300</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>57400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>7900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>6400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>5300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>8400</v>
       </c>
-      <c r="AK100" s="3" t="s">
+      <c r="AL100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9624,8 +9873,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9699,111 +9948,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-56800</v>
+      </c>
+      <c r="E102" s="3">
         <v>22000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-10400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-14700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>49300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>9600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>39700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-46700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-28000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>44500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-20600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-12600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>30700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-7100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>9400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>20600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-16300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>8500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>4400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>46300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-7200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>4900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>700</v>
       </c>
-      <c r="AK102" s="3" t="s">
+      <c r="AL102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
   <si>
     <t>LOVE</t>
   </si>
@@ -656,509 +656,521 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45963</v>
+      </c>
+      <c r="E7" s="2">
         <v>45872</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45781</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45690</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45599</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45508</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45417</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45326</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45228</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45137</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45046</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44955</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44864</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44773</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44682</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44591</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44500</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44409</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44318</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44227</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44136</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44045</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43954</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43863</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43772</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43681</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43590</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43499</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43408</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43317</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43226</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43135</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43037</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42946</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42855</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42582</v>
       </c>
-      <c r="AM7" s="2" t="s">
+      <c r="AN7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>150200</v>
+      </c>
+      <c r="E8" s="3">
         <v>160500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>138400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>241500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>149900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>156600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>132600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>250500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>154000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>154500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>141200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>238500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>134800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>148500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>129400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>196200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>116700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>102400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>82900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>129700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>74700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>61900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>54400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>92200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>52100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>48100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>41000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>64200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>41700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>33200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>26800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>39000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>24400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>20700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>17600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>30500</v>
       </c>
-      <c r="AM8" s="3" t="s">
+      <c r="AN8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>65900</v>
+      </c>
+      <c r="E9" s="3">
         <v>69900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>64000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>95700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>62300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>64200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>60600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>100900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>65600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>62100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>70600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>104800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>69900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>69400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>63400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>173600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>58100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>43400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>36800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>54600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>33400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>30900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>27100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>47000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>25800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>23900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>20000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>28700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>18800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>15400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>12100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>16100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>10700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>9200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>8500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>14700</v>
       </c>
-      <c r="AM9" s="3" t="s">
+      <c r="AN9" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>84200</v>
+      </c>
+      <c r="E10" s="3">
         <v>90600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>74400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>145800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>87600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>92400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>72000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>149600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>88400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>92400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>70600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>133700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>64900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>79100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>66000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>22600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>58600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>59000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>46100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>75100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>41300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>31000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>27300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>45200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>26300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>24200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>21000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>35500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>22900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>17800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>14700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>22900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>13700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>11500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>9100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>15800</v>
       </c>
-      <c r="AM10" s="3" t="s">
+      <c r="AN10" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1198,8 +1210,9 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1311,8 +1324,11 @@
       <c r="AM12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1424,8 +1440,11 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1471,24 +1490,24 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
         <v>-600</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>600</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3">
         <v>200</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1504,8 +1523,8 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1537,110 +1556,113 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E15" s="3">
         <v>3800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>3500</v>
       </c>
       <c r="J15" s="3">
         <v>3500</v>
       </c>
       <c r="K15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L15" s="3">
         <v>3300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>5300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>700</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI15" s="3">
+      <c r="AI15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>800</v>
       </c>
-      <c r="AJ15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1650,8 +1672,11 @@
       <c r="AM15" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN15" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1688,234 +1713,241 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E17" s="3">
         <v>169400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>153300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>193900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>157600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>165000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>150500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>210100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>157600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>155500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>146900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>202000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>144900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>140400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>126900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>169900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>113700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>93400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>80700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>107900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>72200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>63000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>62800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>86800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>59000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>53100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>50300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>55900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>44400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>40200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>32400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>36500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>26500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>23100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>20800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>36500</v>
       </c>
-      <c r="AM17" s="3" t="s">
+      <c r="AN17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-15000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>47600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-17900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>40400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>36500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-10100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>26300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>21800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-8400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-9300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>8300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-5600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-6000</v>
       </c>
-      <c r="AM18" s="3" t="s">
+      <c r="AN18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1955,19 +1987,20 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
@@ -1993,33 +2026,33 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -2027,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="3">
         <v>100</v>
       </c>
       <c r="AB20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC20" s="3">
         <v>200</v>
@@ -2045,10 +2078,10 @@
         <v>200</v>
       </c>
       <c r="AF20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AG20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH20" s="3">
         <v>-100</v>
@@ -2057,132 +2090,138 @@
         <v>-100</v>
       </c>
       <c r="AJ20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-100</v>
       </c>
-      <c r="AL20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM20" s="3" t="s">
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-11300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>51400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-14400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>43800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>39100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>28400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>10600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>23300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>6900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-6200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AM21" s="3" t="s">
+      <c r="AN21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2216,8 +2255,8 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -2289,186 +2328,192 @@
         <v>0</v>
       </c>
       <c r="AL22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="3">
         <v>300</v>
       </c>
-      <c r="AM22" s="3" t="s">
+      <c r="AN22" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>48300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-17100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>41200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>36500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>26300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>9000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>21700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-9100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-6300</v>
       </c>
-      <c r="AM23" s="3" t="s">
+      <c r="AN23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-4200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>10200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1000</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-7900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
@@ -2508,8 +2553,8 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
-      <c r="AJ24" s="3" t="s">
-        <v>3</v>
+      <c r="AJ24" s="3">
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="s">
         <v>3</v>
@@ -2520,8 +2565,11 @@
       <c r="AM24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2633,234 +2681,243 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>35300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>31000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>26200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>34200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>8400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>21700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>5400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-9100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>8400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-5700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-6300</v>
       </c>
-      <c r="AM26" s="3" t="s">
+      <c r="AN26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>35300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-13000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>31000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>26200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>34200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>8400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>21700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>5400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-9100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>8400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-33700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-6400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-6300</v>
       </c>
-      <c r="AM27" s="3" t="s">
+      <c r="AN27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2972,8 +3029,11 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3085,8 +3145,11 @@
       <c r="AM29" s="3">
         <v>0</v>
       </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3198,8 +3261,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3311,19 +3377,22 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
@@ -3349,33 +3418,33 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -3383,13 +3452,13 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3">
         <v>-100</v>
       </c>
       <c r="AB32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AC32" s="3">
         <v>-200</v>
@@ -3401,10 +3470,10 @@
         <v>-200</v>
       </c>
       <c r="AF32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AG32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH32" s="3">
         <v>100</v>
@@ -3413,132 +3482,138 @@
         <v>100</v>
       </c>
       <c r="AJ32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3">
         <v>100</v>
       </c>
-      <c r="AL32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM32" s="3" t="s">
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>35300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-13000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>31000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>26200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>34200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>8400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>21700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>5400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-9100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>8400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-33700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-6400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-6300</v>
       </c>
-      <c r="AM33" s="3" t="s">
+      <c r="AN33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3650,239 +3725,248 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>35300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-13000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>31000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>26200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>34200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>8400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>21700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>5400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-9100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>8400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-33700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-6400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-6300</v>
       </c>
-      <c r="AM35" s="3" t="s">
+      <c r="AN35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45963</v>
+      </c>
+      <c r="E38" s="2">
         <v>45872</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45781</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45690</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45599</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45508</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45417</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45326</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45228</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45137</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45046</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44955</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44864</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44773</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44682</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44591</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44500</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44409</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44318</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44227</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44136</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44045</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43954</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43863</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43772</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43681</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43590</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43499</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43408</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43317</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43226</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43135</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43037</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42946</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42855</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42582</v>
       </c>
-      <c r="AM38" s="2" t="s">
+      <c r="AN38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3922,8 +4006,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3963,107 +4048,108 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E41" s="3">
         <v>34200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>26900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>83700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>61700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>72100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>72400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>87000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>37700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>54700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>45100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>43500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>64400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>92400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>47900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>68500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>65700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>78300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>47700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>54800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>45500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>48500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>27900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>44200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>35700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>49100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>44700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>48200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>9200</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ41" s="3" t="s">
         <v>3</v>
       </c>
@@ -4076,8 +4162,11 @@
       <c r="AM41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4189,107 +4278,110 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E43" s="3">
         <v>14100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>16800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>13500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>15400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>9800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2800</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4302,107 +4394,110 @@
       <c r="AM43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>129700</v>
+      </c>
+      <c r="E44" s="3">
         <v>124000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>124900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>124300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>113400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>88300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>94700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>98400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>116600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>105000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>104500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>119600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>154500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>145700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>123000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>108500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>94500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>75000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>56000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>50400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>57800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>41000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>33400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>36400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>50200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>40700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>30900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>26200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>24600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>20200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>13900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>11600</v>
       </c>
-      <c r="AI44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4415,107 +4510,110 @@
       <c r="AM44" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN44" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E45" s="3">
         <v>3300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3800</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3">
         <v>5100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>35600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>31200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>11400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>11600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>6300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>6300</v>
-      </c>
-      <c r="AF45" s="3">
-        <v>5800</v>
       </c>
       <c r="AG45" s="3">
         <v>5800</v>
       </c>
       <c r="AH45" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AI45" s="3">
         <v>6100</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4528,107 +4626,110 @@
       <c r="AM45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>186000</v>
+      </c>
+      <c r="E46" s="3">
         <v>189800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>181500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>246600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>209900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>194200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>190800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>214400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>184300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>183600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>181500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>187700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>209300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>203500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>206200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>221700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>163600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>161400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>140200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>143400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>123500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>107800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>91900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>100200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>95400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>97500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>78000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>85100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>78500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>78300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>24900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>29700</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4641,8 +4742,11 @@
       <c r="AM46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4679,8 +4783,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4754,107 +4858,110 @@
       <c r="AM47" s="3">
         <v>0</v>
       </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>249800</v>
+      </c>
+      <c r="E48" s="3">
         <v>249900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>249500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>235700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>234900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>236100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>239500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>226700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>212300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>212400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>202800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>188300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>179500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>155300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>145400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>135000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>127700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>118400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>117600</v>
-      </c>
-      <c r="V48" s="3">
-        <v>25900</v>
       </c>
       <c r="W48" s="3">
         <v>25900</v>
       </c>
       <c r="X48" s="3">
+        <v>25900</v>
+      </c>
+      <c r="Y48" s="3">
         <v>25700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>24400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>23800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>21800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>18600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>17100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>15700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>13200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>11000</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4867,25 +4974,28 @@
       <c r="AM48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E49" s="3">
         <v>2000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1900</v>
-      </c>
-      <c r="F49" s="3">
-        <v>1700</v>
       </c>
       <c r="G49" s="3">
         <v>1700</v>
       </c>
       <c r="H49" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="I49" s="3">
         <v>1600</v>
@@ -4906,10 +5016,10 @@
         <v>1600</v>
       </c>
       <c r="O49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P49" s="3">
         <v>2900</v>
-      </c>
-      <c r="P49" s="3">
-        <v>3000</v>
       </c>
       <c r="Q49" s="3">
         <v>3000</v>
@@ -4918,55 +5028,55 @@
         <v>3000</v>
       </c>
       <c r="S49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="T49" s="3">
         <v>1500</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1300</v>
       </c>
       <c r="U49" s="3">
         <v>1300</v>
       </c>
       <c r="V49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="W49" s="3">
         <v>1700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1200</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>1100</v>
       </c>
       <c r="AD49" s="3">
         <v>1100</v>
       </c>
       <c r="AE49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF49" s="3">
         <v>1000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>800</v>
-      </c>
-      <c r="AG49" s="3">
-        <v>700</v>
       </c>
       <c r="AH49" s="3">
         <v>700</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>3</v>
+      <c r="AI49" s="3">
+        <v>700</v>
       </c>
       <c r="AJ49" s="3" t="s">
         <v>3</v>
@@ -4980,8 +5090,11 @@
       <c r="AM49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5093,8 +5206,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5206,64 +5322,67 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E52" s="3">
         <v>30700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>32000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>32900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>34100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>32300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>30400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>28700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>26900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>22400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10800</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
       <c r="T52" s="3">
         <v>0</v>
       </c>
       <c r="U52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V52" s="3">
         <v>100</v>
@@ -5275,13 +5394,13 @@
         <v>100</v>
       </c>
       <c r="Y52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z52" s="3">
         <v>200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>100</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>200</v>
       </c>
       <c r="AB52" s="3">
         <v>200</v>
@@ -5296,16 +5415,16 @@
         <v>200</v>
       </c>
       <c r="AF52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AG52" s="3">
         <v>300</v>
       </c>
       <c r="AH52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI52" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="AI52" s="3">
+        <v>0</v>
       </c>
       <c r="AJ52" s="3" t="s">
         <v>3</v>
@@ -5319,8 +5438,11 @@
       <c r="AM52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5432,107 +5554,110 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>495500</v>
+      </c>
+      <c r="E54" s="3">
         <v>493700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>483700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>532300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>499700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>481100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>477200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>482200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>436300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>433600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>421200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>408600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>401100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>368900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>363600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>369100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>292800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>281300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>259200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>171000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>151100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>135300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>118100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>125700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>118700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>119300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>98800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>105000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>96800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>95100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>39100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>41400</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5545,8 +5670,11 @@
       <c r="AM54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5586,8 +5714,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5627,107 +5756,108 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E57" s="3">
         <v>36000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>25000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>51800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>48700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>28500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>28100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>28800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>37200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>33900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>30100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>24600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>47300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>34200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>29800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>33200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>25400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>25900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>17700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>24300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>25200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>24500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>17400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>19900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>19000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>17700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>19800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>16800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>16900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>15300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>12200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>12700</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5740,47 +5870,50 @@
       <c r="AM57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E58" s="3">
         <v>22800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>22600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>22700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>21200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>19000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>18500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>17600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>17000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>16100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>16900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13100</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5838,8 +5971,8 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>3</v>
+      <c r="AI58" s="3">
+        <v>0</v>
       </c>
       <c r="AJ58" s="3" t="s">
         <v>3</v>
@@ -5853,107 +5986,110 @@
       <c r="AM58" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN58" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E59" s="3">
         <v>19700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>31900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>22900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>64100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>58600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>69600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>81400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>56100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>54700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>46000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>32000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>34300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>23600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>12500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>12800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>7700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>6200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>5900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4000</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5966,107 +6102,110 @@
       <c r="AM59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>137000</v>
+      </c>
+      <c r="E60" s="3">
         <v>125100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>113100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>155100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>141100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>115100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>105500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>106400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>105900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>97300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>89100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>82000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>111400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>92900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>99400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>114700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>81600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>80600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>63700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>56300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>59500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>48000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>32300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>32400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>31800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>27100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>27400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>24600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>25100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>21500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>18200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>16700</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ60" s="3" t="s">
         <v>3</v>
       </c>
@@ -6079,47 +6218,50 @@
       <c r="AM60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>168800</v>
+      </c>
+      <c r="E61" s="3">
         <v>170700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>169000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>160400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>161700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>163400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>165900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>157900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>144900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>149400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>142800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>133500</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -6172,11 +6314,11 @@
         <v>0</v>
       </c>
       <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>1500</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
@@ -6192,8 +6334,11 @@
       <c r="AM61" s="3">
         <v>0</v>
       </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6207,7 +6352,7 @@
         <v>400</v>
       </c>
       <c r="G62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H62" s="3">
         <v>500</v>
@@ -6218,8 +6363,8 @@
       <c r="J62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
+      <c r="K62" s="3">
+        <v>500</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
@@ -6230,69 +6375,69 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
         <v>130200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>109900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>103500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>96600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>90700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>83700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>84700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1700</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>1600</v>
       </c>
       <c r="AD62" s="3">
         <v>1600</v>
       </c>
       <c r="AE62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AF62" s="3">
         <v>1400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1100</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ62" s="3" t="s">
         <v>3</v>
       </c>
@@ -6305,8 +6450,11 @@
       <c r="AM62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6418,8 +6566,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6531,8 +6682,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6644,107 +6798,110 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>306200</v>
+      </c>
+      <c r="E66" s="3">
         <v>296200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>282500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>315900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>303200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>278900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>271900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>264700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>250800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>246800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>232000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>215500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>241600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>202700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>202900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>211300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>172200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>164300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>148500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>63100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>65900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>53500</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>35500</v>
       </c>
       <c r="Z66" s="3">
         <v>35500</v>
       </c>
       <c r="AA66" s="3">
+        <v>35500</v>
+      </c>
+      <c r="AB66" s="3">
         <v>34300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>28700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>29000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>26200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>26500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>22900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>20800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>17800</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6757,8 +6914,11 @@
       <c r="AM66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6798,8 +6958,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6911,8 +7072,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7024,8 +7188,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7137,8 +7304,11 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7250,107 +7420,110 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E72" s="3">
         <v>2300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>25800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>21400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>34400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>10500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-15700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-14200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-15900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-50200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-52900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-61400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-63400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-85100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-87600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-86500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-78200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-83600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-76800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-72100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-63000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-71400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-68900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-61900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-56300</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7363,8 +7536,11 @@
       <c r="AM72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7476,8 +7652,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7589,8 +7768,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7702,107 +7884,110 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>189300</v>
+      </c>
+      <c r="E76" s="3">
         <v>197500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>201200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>216400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>196500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>202100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>205300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>217500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>185500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>186800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>189300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>193100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>159400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>166200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>160700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>157800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>120600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>116900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>110700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>107900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>85300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>81800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>82600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>90200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>84400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>90600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>69700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>78800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>70300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>72200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>18300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>23600</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7815,8 +8000,11 @@
       <c r="AM76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7928,239 +8116,248 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45963</v>
+      </c>
+      <c r="E80" s="2">
         <v>45872</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45781</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45690</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45599</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45508</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45417</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45326</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45228</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45137</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45046</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44955</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44864</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44773</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44682</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44591</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44500</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44409</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44318</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44227</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44136</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44045</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43954</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43863</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43772</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43681</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43590</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43499</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43408</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43317</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43226</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43135</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43037</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42946</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42855</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42582</v>
       </c>
-      <c r="AM80" s="2" t="s">
+      <c r="AN80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>35300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-13000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>31000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>26200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>34200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>8400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>21700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>5400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-9100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>8400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-33700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-6400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-6300</v>
       </c>
-      <c r="AM81" s="3" t="s">
+      <c r="AN81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8200,8 +8397,9 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8209,112 +8407,115 @@
         <v>3600</v>
       </c>
       <c r="E83" s="3">
-        <v>3400</v>
+        <v>3600</v>
       </c>
       <c r="F83" s="3">
         <v>3400</v>
       </c>
       <c r="G83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H83" s="3">
         <v>3200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>800</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>700</v>
       </c>
       <c r="AH83" s="3">
         <v>700</v>
       </c>
       <c r="AI83" s="3">
+        <v>700</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>800</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>300</v>
       </c>
       <c r="AK83" s="3">
         <v>300</v>
       </c>
       <c r="AL83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AM83" s="3">
         <v>1200</v>
       </c>
-      <c r="AM83" s="3" t="s">
+      <c r="AN83" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8426,8 +8627,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8539,8 +8743,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8652,8 +8859,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8765,8 +8975,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8878,121 +9091,127 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E89" s="3">
         <v>12200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-41400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>44000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>56300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>21100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>47000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-37600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-21800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>49200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-15900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>10400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-9600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>33600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-5100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>12600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>25200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-14900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-8200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-7700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>6800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-4600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-6300</v>
       </c>
-      <c r="AM89" s="3" t="s">
+      <c r="AN89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9032,121 +9251,125 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AM91" s="3" t="s">
+      <c r="AN91" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9258,8 +9481,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9371,121 +9597,127 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3100</v>
-      </c>
-      <c r="V94" s="3">
-        <v>-1900</v>
       </c>
       <c r="W94" s="3">
         <v>-1900</v>
       </c>
       <c r="X94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AI94" s="3">
-        <v>-2300</v>
       </c>
       <c r="AJ94" s="3">
         <v>-2300</v>
       </c>
       <c r="AK94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AM94" s="3" t="s">
+      <c r="AN94" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9525,8 +9757,9 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9563,8 +9796,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9638,8 +9871,11 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9751,8 +9987,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9864,8 +10103,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9977,121 +10219,127 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-16500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-400</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-3100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-500</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-100</v>
       </c>
       <c r="O100" s="3">
         <v>-100</v>
       </c>
       <c r="P100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-200</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>-200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-900</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>25400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-300</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>57400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>6400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>5300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>8400</v>
       </c>
-      <c r="AM100" s="3" t="s">
+      <c r="AN100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10128,8 +10376,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10203,117 +10451,123 @@
       <c r="AM101" s="3">
         <v>0</v>
       </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E102" s="3">
         <v>7300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-56800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>22000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-10400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>49300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>9600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>39700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-46700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-28000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>44500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-20600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-12600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>30700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-7100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>9400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>20600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-16300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>8500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-13400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>4400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>46300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-7200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>3500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>4900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>700</v>
       </c>
-      <c r="AM102" s="3" t="s">
+      <c r="AN102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LOVE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
   <si>
     <t>LOVE</t>
   </si>
@@ -656,521 +656,534 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46054</v>
+      </c>
+      <c r="E7" s="2">
         <v>45963</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45872</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45781</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45690</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45599</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45508</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45417</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45326</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45228</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45137</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45046</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44955</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44864</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44773</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44682</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44591</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44500</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44409</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44318</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44227</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44136</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44045</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43954</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43863</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43772</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43681</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43590</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43499</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43408</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43317</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43226</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43135</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43037</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42946</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42855</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42582</v>
       </c>
-      <c r="AN7" s="2" t="s">
+      <c r="AO7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>248000</v>
+      </c>
+      <c r="E8" s="3">
         <v>150200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>160500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>138400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>241500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>149900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>156600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>132600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>250500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>154000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>154500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>141200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>238500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>134800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>148500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>129400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>196200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>116700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>102400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>82900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>129700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>74700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>61900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>54400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>92200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>52100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>48100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>41000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>64200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>41700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>33200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>26800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>39000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>24400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>20700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>17600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>30500</v>
       </c>
-      <c r="AN8" s="3" t="s">
+      <c r="AO8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>104000</v>
+      </c>
+      <c r="E9" s="3">
         <v>65900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>69900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>64000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>95700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>62300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>64200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>60600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>100900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>65600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>62100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>70600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>104800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>69900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>69400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>63400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>173600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>58100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>43400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>36800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>54600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>33400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>30900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>27100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>47000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>25800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>23900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>20000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>28700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>18800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>15400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>12100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>16100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>10700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>9200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>8500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>14700</v>
       </c>
-      <c r="AN9" s="3" t="s">
+      <c r="AO9" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E10" s="3">
         <v>84200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>90600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>74400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>145800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>87600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>92400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>72000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>149600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>88400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>92400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>70600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>133700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>64900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>79100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>66000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>22600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>58600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>59000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>46100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>75100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>41300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>31000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>27300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>45200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>26300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>24200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>21000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>35500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>22900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>17800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>14700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>22900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>13700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>11500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>9100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>15800</v>
       </c>
-      <c r="AN10" s="3" t="s">
+      <c r="AO10" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1211,8 +1224,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1327,8 +1341,11 @@
       <c r="AN12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1443,13 +1460,16 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-1500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1493,24 +1513,24 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
         <v>-600</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3">
         <v>200</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1526,8 +1546,8 @@
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1559,113 +1579,116 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E15" s="3">
         <v>4000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>3500</v>
       </c>
       <c r="K15" s="3">
         <v>3500</v>
       </c>
       <c r="L15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M15" s="3">
         <v>3300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>5300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>1100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>700</v>
       </c>
-      <c r="AI15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ15" s="3">
+      <c r="AJ15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK15" s="3">
         <v>800</v>
       </c>
-      <c r="AK15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1675,8 +1698,11 @@
       <c r="AN15" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO15" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1714,240 +1740,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>204600</v>
+      </c>
+      <c r="E17" s="3">
         <v>166000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>169400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>153300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>193900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>157600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>165000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>150500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>210100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>157600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>155500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>146900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>202000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>144900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>140400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>126900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>169900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>113700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>93400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>80700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>107900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>72200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>63000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>62800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>86800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>59000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>53100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>50300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>55900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>44400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>40200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>32400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>36500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>26500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>23100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>20800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>36500</v>
       </c>
-      <c r="AN17" s="3" t="s">
+      <c r="AO17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>43400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-15800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-15000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>47600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-17900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>40400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>36500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-10100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>26300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>21800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-8400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>5400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-9300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>8300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-7000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-5600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-3200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-6000</v>
       </c>
-      <c r="AN18" s="3" t="s">
+      <c r="AO18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1988,25 +2021,26 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -2029,33 +2063,33 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
@@ -2063,13 +2097,13 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="3">
         <v>100</v>
       </c>
       <c r="AC20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD20" s="3">
         <v>200</v>
@@ -2081,10 +2115,10 @@
         <v>200</v>
       </c>
       <c r="AG20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AH20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3">
         <v>-100</v>
@@ -2093,135 +2127,141 @@
         <v>-100</v>
       </c>
       <c r="AK20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AL20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="3">
         <v>-100</v>
       </c>
-      <c r="AM20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN20" s="3" t="s">
+      <c r="AN20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>47200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-11800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-5000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>51400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-14400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>43800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>39100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>28400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>10600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>23300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-6700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>6900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-6200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-3000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AN21" s="3" t="s">
+      <c r="AO21" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2258,8 +2298,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2331,192 +2371,198 @@
         <v>0</v>
       </c>
       <c r="AM22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="3">
         <v>300</v>
       </c>
-      <c r="AN22" s="3" t="s">
+      <c r="AO22" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-15600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>48300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>41200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>36500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>26300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>9000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>21700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-6700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-9100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>8500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-7000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-6300</v>
       </c>
-      <c r="AN23" s="3" t="s">
+      <c r="AO23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-5000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-3800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-4200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>10200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1000</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-1300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-7900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
@@ -2556,8 +2602,8 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
-      <c r="AK24" s="3" t="s">
-        <v>3</v>
+      <c r="AK24" s="3">
+        <v>0</v>
       </c>
       <c r="AL24" s="3" t="s">
         <v>3</v>
@@ -2568,8 +2614,11 @@
       <c r="AN24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2684,240 +2733,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>35300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>31000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>26200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>34200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>8400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>21700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-6700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-9100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>8400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-7000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-5700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-6300</v>
       </c>
-      <c r="AN26" s="3" t="s">
+      <c r="AO26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>35300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>31000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>26200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>34200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>8400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>21700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-6700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-9100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>8400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-33700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-6400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-6300</v>
       </c>
-      <c r="AN27" s="3" t="s">
+      <c r="AO27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3032,8 +3090,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3148,8 +3209,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3264,8 +3328,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3380,25 +3447,28 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
         <v>0</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -3421,33 +3491,33 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -3455,13 +3525,13 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="3">
         <v>-100</v>
       </c>
       <c r="AC32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AD32" s="3">
         <v>-200</v>
@@ -3473,10 +3543,10 @@
         <v>-200</v>
       </c>
       <c r="AG32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AH32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3">
         <v>100</v>
@@ -3485,135 +3555,141 @@
         <v>100</v>
       </c>
       <c r="AK32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AL32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="3">
         <v>100</v>
       </c>
-      <c r="AM32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN32" s="3" t="s">
+      <c r="AN32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>35300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>31000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>26200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>34200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>8400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>21700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-6700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-9100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>8400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-33700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-6400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-6300</v>
       </c>
-      <c r="AN33" s="3" t="s">
+      <c r="AO33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3728,245 +3804,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>35300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>31000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>26200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>34200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>8400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>21700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-6700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-9100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>8400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-33700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-6400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-6300</v>
       </c>
-      <c r="AN35" s="3" t="s">
+      <c r="AO35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46054</v>
+      </c>
+      <c r="E38" s="2">
         <v>45963</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45872</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45781</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45690</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45599</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45508</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45417</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45326</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45228</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45137</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45046</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44955</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44864</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44773</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44682</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44591</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44500</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44409</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44318</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44227</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44136</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44045</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43954</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43863</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43772</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43681</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43590</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43499</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43408</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43317</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43226</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43135</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43037</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42946</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42855</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42582</v>
       </c>
-      <c r="AN38" s="2" t="s">
+      <c r="AO38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4007,8 +4092,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4049,110 +4135,111 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>101900</v>
+      </c>
+      <c r="E41" s="3">
         <v>23700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>34200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>26900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>83700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>61700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>72100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>72400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>87000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>37700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>54700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>45100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>43500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>17700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>64400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>92400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>47900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>68500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>65700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>78300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>47700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>54800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>45500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>48500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>27900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>44200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>35700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>49100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>44700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>48200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>9200</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK41" s="3" t="s">
         <v>3</v>
       </c>
@@ -4165,8 +4252,11 @@
       <c r="AN41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4281,110 +4371,113 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E43" s="3">
         <v>17000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>16100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>14800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>18400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>9800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>8600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4397,110 +4490,113 @@
       <c r="AN43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>106300</v>
+      </c>
+      <c r="E44" s="3">
         <v>129700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>124000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>124900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>124300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>113400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>88300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>94700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>98400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>116600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>105000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>104500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>119600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>154500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>145700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>123000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>108500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>94500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>75000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>56000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>50400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>57800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>41000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>33400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>36400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>50200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>40700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>30900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>26200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>24600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>20200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>13900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>11600</v>
       </c>
-      <c r="AJ44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4513,110 +4609,113 @@
       <c r="AN44" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO44" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E45" s="3">
         <v>2500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3800</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>5100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>35600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>31200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>11400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>11600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>10900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>8700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>6300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>6300</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>5800</v>
       </c>
       <c r="AH45" s="3">
         <v>5800</v>
       </c>
       <c r="AI45" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>6100</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4629,110 +4728,113 @@
       <c r="AN45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>236600</v>
+      </c>
+      <c r="E46" s="3">
         <v>186000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>189800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>181500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>246600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>209900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>194200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>190800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>214400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>184300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>183600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>181500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>187700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>209300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>203500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>206200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>221700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>163600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>161400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>140200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>143400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>123500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>107800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>91900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>100200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>95400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>97500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>78000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>85100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>78500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>78300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>24900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>29700</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4745,8 +4847,11 @@
       <c r="AN46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4786,8 +4891,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4861,110 +4966,113 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>249700</v>
+      </c>
+      <c r="E48" s="3">
         <v>249800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>249900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>249500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>235700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>234900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>236100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>239500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>226700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>212300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>212400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>202800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>188300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>179500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>155300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>145400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>135000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>127700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>118400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>117600</v>
-      </c>
-      <c r="W48" s="3">
-        <v>25900</v>
       </c>
       <c r="X48" s="3">
         <v>25900</v>
       </c>
       <c r="Y48" s="3">
+        <v>25900</v>
+      </c>
+      <c r="Z48" s="3">
         <v>25700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>24400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>23800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>21800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>20400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>18600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>17100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>15700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>13200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4977,28 +5085,31 @@
       <c r="AN48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E49" s="3">
         <v>2200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1900</v>
-      </c>
-      <c r="G49" s="3">
-        <v>1700</v>
       </c>
       <c r="H49" s="3">
         <v>1700</v>
       </c>
       <c r="I49" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="J49" s="3">
         <v>1600</v>
@@ -5019,10 +5130,10 @@
         <v>1600</v>
       </c>
       <c r="P49" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q49" s="3">
         <v>2900</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>3000</v>
       </c>
       <c r="R49" s="3">
         <v>3000</v>
@@ -5031,55 +5142,55 @@
         <v>3000</v>
       </c>
       <c r="T49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="U49" s="3">
         <v>1500</v>
-      </c>
-      <c r="U49" s="3">
-        <v>1300</v>
       </c>
       <c r="V49" s="3">
         <v>1300</v>
       </c>
       <c r="W49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="X49" s="3">
         <v>1700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1200</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>1100</v>
       </c>
       <c r="AE49" s="3">
         <v>1100</v>
       </c>
       <c r="AF49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AG49" s="3">
         <v>1000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>800</v>
-      </c>
-      <c r="AH49" s="3">
-        <v>700</v>
       </c>
       <c r="AI49" s="3">
         <v>700</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>3</v>
+      <c r="AJ49" s="3">
+        <v>700</v>
       </c>
       <c r="AK49" s="3" t="s">
         <v>3</v>
@@ -5093,8 +5204,11 @@
       <c r="AN49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5209,8 +5323,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5325,67 +5442,70 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E52" s="3">
         <v>31100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>30700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>32000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>32900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>34100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>32300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>30400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>26900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>22400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10800</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
-      </c>
       <c r="U52" s="3">
         <v>0</v>
       </c>
       <c r="V52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W52" s="3">
         <v>100</v>
@@ -5397,13 +5517,13 @@
         <v>100</v>
       </c>
       <c r="Z52" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA52" s="3">
         <v>200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>100</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>200</v>
       </c>
       <c r="AC52" s="3">
         <v>200</v>
@@ -5418,16 +5538,16 @@
         <v>200</v>
       </c>
       <c r="AG52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AH52" s="3">
         <v>300</v>
       </c>
       <c r="AI52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ52" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
       </c>
       <c r="AK52" s="3" t="s">
         <v>3</v>
@@ -5441,8 +5561,11 @@
       <c r="AN52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5557,110 +5680,113 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>534700</v>
+      </c>
+      <c r="E54" s="3">
         <v>495500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>493700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>483700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>532300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>499700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>481100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>477200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>482200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>436300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>433600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>421200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>408600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>401100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>368900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>363600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>369100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>292800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>281300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>259200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>171000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>151100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>135300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>118100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>125700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>118700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>119300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>98800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>105000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>96800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>95100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>39100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>41400</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5673,8 +5799,11 @@
       <c r="AN54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5715,8 +5844,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5757,110 +5887,111 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E57" s="3">
         <v>45500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>36000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>25000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>51800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>48700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>28500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>28100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>28800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>37200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>33900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>30100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>24600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>47300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>34200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>29800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>33200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>25400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>25900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>17700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>24300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>25200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>24500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>17400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>19900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>19000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>17700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>19800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>16800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>16900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>15300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>12200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>12700</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5873,50 +6004,53 @@
       <c r="AN57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E58" s="3">
         <v>22700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>22800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>22600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>22700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>21200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>18500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>17600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>17000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>16100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>16900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13100</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -5974,8 +6108,8 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>3</v>
+      <c r="AJ58" s="3">
+        <v>0</v>
       </c>
       <c r="AK58" s="3" t="s">
         <v>3</v>
@@ -5989,110 +6123,113 @@
       <c r="AN58" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO58" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E59" s="3">
         <v>14500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>19700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>31900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>21200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>20100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>64100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>58600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>69600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>81400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>56100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>54700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>46000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>32000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>34300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>23600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>12500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>12800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>6200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>5900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK59" s="3" t="s">
         <v>3</v>
       </c>
@@ -6105,110 +6242,113 @@
       <c r="AN59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>147100</v>
+      </c>
+      <c r="E60" s="3">
         <v>137000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>125100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>113100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>155100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>141100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>115100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>105500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>106400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>105900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>97300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>89100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>82000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>111400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>92900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>99400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>114700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>81600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>80600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>63700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>56300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>59500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>48000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>32300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>32400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>31800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>27100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>27400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>24600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>25100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>21500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>18200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>16700</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK60" s="3" t="s">
         <v>3</v>
       </c>
@@ -6221,50 +6361,53 @@
       <c r="AN60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>168400</v>
+      </c>
+      <c r="E61" s="3">
         <v>168800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>170700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>169000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>160400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>161700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>163400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>165900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>157900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>144900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>149400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>142800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>133500</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -6317,11 +6460,11 @@
         <v>0</v>
       </c>
       <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
         <v>1500</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
@@ -6337,13 +6480,16 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E62" s="3">
         <v>400</v>
@@ -6355,7 +6501,7 @@
         <v>400</v>
       </c>
       <c r="H62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I62" s="3">
         <v>500</v>
@@ -6366,8 +6512,8 @@
       <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
+      <c r="L62" s="3">
+        <v>500</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
@@ -6378,69 +6524,69 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>130200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>109900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>103500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>96600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>90700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>83700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>84700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1700</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>1600</v>
       </c>
       <c r="AE62" s="3">
         <v>1600</v>
       </c>
       <c r="AF62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AG62" s="3">
         <v>1400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK62" s="3" t="s">
         <v>3</v>
       </c>
@@ -6453,8 +6599,11 @@
       <c r="AN62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6569,8 +6718,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6685,8 +6837,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6801,110 +6956,113 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>316000</v>
+      </c>
+      <c r="E66" s="3">
         <v>306200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>296200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>282500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>315900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>303200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>278900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>271900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>264700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>250800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>246800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>232000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>215500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>241600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>202700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>202900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>211300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>172200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>164300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>148500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>63100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>65900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>53500</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>35500</v>
       </c>
       <c r="AA66" s="3">
         <v>35500</v>
       </c>
       <c r="AB66" s="3">
+        <v>35500</v>
+      </c>
+      <c r="AC66" s="3">
         <v>34300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>28700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>29000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>26200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>26500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>22900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>20800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>17800</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6917,8 +7075,11 @@
       <c r="AN66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6959,8 +7120,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7075,8 +7237,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7191,8 +7356,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7307,8 +7475,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7423,110 +7594,113 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-8200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>25800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>21400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>34400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-8300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-14200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-15900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-50200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-52900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-61400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-63400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-85100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-87600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-86500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-78200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-83600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-76800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-72100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-63000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-71400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-68900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-61900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-56300</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7539,8 +7713,11 @@
       <c r="AN72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7655,8 +7832,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7771,8 +7951,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7887,110 +8070,113 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>218700</v>
+      </c>
+      <c r="E76" s="3">
         <v>189300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>197500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>201200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>216400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>196500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>202100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>205300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>217500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>185500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>186800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>189300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>193100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>159400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>166200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>160700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>157800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>120600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>116900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>110700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>107900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>85300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>81800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>82600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>90200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>84400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>90600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>69700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>78800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>70300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>72200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>18300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>23600</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK76" s="3" t="s">
         <v>3</v>
       </c>
@@ -8003,8 +8189,11 @@
       <c r="AN76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AO76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8119,245 +8308,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46054</v>
+      </c>
+      <c r="E80" s="2">
         <v>45963</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45872</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45781</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45690</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45599</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45508</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45417</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45326</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45228</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45137</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45046</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44955</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44864</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44773</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44682</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44591</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44500</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44409</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44318</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44227</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44136</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44045</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43954</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43863</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43772</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43681</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43590</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43499</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43408</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43317</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43226</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43135</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43037</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42946</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42855</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42582</v>
       </c>
-      <c r="AN80" s="2" t="s">
+      <c r="AO80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>35300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>31000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>26200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>34200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>8400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>21700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-6700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-9100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>8400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-33700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-6400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-6300</v>
       </c>
-      <c r="AN81" s="3" t="s">
+      <c r="AO81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8398,124 +8596,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="E83" s="3">
         <v>3600</v>
       </c>
       <c r="F83" s="3">
-        <v>3400</v>
+        <v>3600</v>
       </c>
       <c r="G83" s="3">
         <v>3400</v>
       </c>
       <c r="H83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I83" s="3">
         <v>3200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>800</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>700</v>
       </c>
       <c r="AI83" s="3">
         <v>700</v>
       </c>
       <c r="AJ83" s="3">
+        <v>700</v>
+      </c>
+      <c r="AK83" s="3">
         <v>800</v>
-      </c>
-      <c r="AK83" s="3">
-        <v>300</v>
       </c>
       <c r="AL83" s="3">
         <v>300</v>
       </c>
       <c r="AM83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AN83" s="3">
         <v>1200</v>
       </c>
-      <c r="AN83" s="3" t="s">
+      <c r="AO83" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8630,8 +8832,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8746,8 +8951,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8862,8 +9070,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8978,8 +9189,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9094,124 +9308,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>83400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>12200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-41400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>44000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>56300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>21100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>47000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-37600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-21800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>49200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-15900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>10400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-9600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>33600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>12600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>25200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-13400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-14900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-8200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>7200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-7700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-4600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-6300</v>
       </c>
-      <c r="AN89" s="3" t="s">
+      <c r="AO89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9252,124 +9472,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AN91" s="3" t="s">
+      <c r="AO91" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9484,8 +9708,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9600,124 +9827,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3100</v>
-      </c>
-      <c r="W94" s="3">
-        <v>-1900</v>
       </c>
       <c r="X94" s="3">
         <v>-1900</v>
       </c>
       <c r="Y94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AJ94" s="3">
-        <v>-2300</v>
       </c>
       <c r="AK94" s="3">
         <v>-2300</v>
       </c>
       <c r="AL94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AM94" s="3">
         <v>-800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AN94" s="3" t="s">
+      <c r="AO94" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9758,8 +9991,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9799,8 +10033,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9874,8 +10108,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9990,8 +10227,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10106,8 +10346,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10222,8 +10465,11 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10231,115 +10477,118 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-16500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-400</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-3100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-500</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-100</v>
       </c>
       <c r="P100" s="3">
         <v>-100</v>
       </c>
       <c r="Q100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R100" s="3">
         <v>-1500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-200</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-900</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>25400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-300</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>57400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>7900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>6400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>5300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>8400</v>
       </c>
-      <c r="AN100" s="3" t="s">
+      <c r="AO100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10379,8 +10628,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10454,120 +10703,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>78100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-10500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-56800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>22000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>49300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-17000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>39700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-46700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-28000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>44500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-20600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-12600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>30700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>9400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>20600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-16300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>8500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-13400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>4400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>46300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-7200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>4900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>700</v>
       </c>
-      <c r="AN102" s="3" t="s">
+      <c r="AO102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
